--- a/ZAF_WB_timeseries.xlsx
+++ b/ZAF_WB_timeseries.xlsx
@@ -14,21 +14,117 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+  <si>
+    <t>Bank capital to assets ratio (%)</t>
+  </si>
+  <si>
+    <t>Bank liquid reserves to bank assets (%)</t>
+  </si>
+  <si>
+    <t>Bank nonperforming loans (% of gross loans)</t>
+  </si>
+  <si>
+    <t>Control of Corruption</t>
+  </si>
+  <si>
+    <t>Current account balance (% of GDP)</t>
+  </si>
+  <si>
+    <t>Debt (% of GDP)</t>
+  </si>
+  <si>
+    <t>Domestic credit to private sector (% of GDP)</t>
+  </si>
+  <si>
+    <t>Exports of goods and services (% of GDP)</t>
+  </si>
+  <si>
+    <t>External debt stocks (% of GNI)</t>
+  </si>
+  <si>
+    <t>External debt stocks (current US$)</t>
+  </si>
   <si>
     <t>GDP growth (annual %)</t>
   </si>
   <si>
+    <t>GDP per capita (PPP, international $)</t>
+  </si>
+  <si>
+    <t>GDP per capita (current US$)</t>
+  </si>
+  <si>
+    <t>GDP per capita growth (annual %)</t>
+  </si>
+  <si>
+    <t>Gini index</t>
+  </si>
+  <si>
+    <t>Government Effectiveness</t>
+  </si>
+  <si>
+    <t>Government consumption (% of GDP)</t>
+  </si>
+  <si>
+    <t>Government expenditure (% of GDP)</t>
+  </si>
+  <si>
+    <t>Government revenue (% of GDP)</t>
+  </si>
+  <si>
+    <t>Imports of goods and services (% of GDP)</t>
+  </si>
+  <si>
     <t>Inflation, consumer prices (annual %)</t>
   </si>
   <si>
     <t>Interest payments (% of GDP)</t>
   </si>
   <si>
+    <t>Life expectancy at birth (years)</t>
+  </si>
+  <si>
+    <t>Military expenditure (% of GDP)</t>
+  </si>
+  <si>
+    <t>Net lending/borrowing (% of GDP)</t>
+  </si>
+  <si>
+    <t>Political Stability and Absence of Violence</t>
+  </si>
+  <si>
+    <t>Population, total</t>
+  </si>
+  <si>
+    <t>Poverty headcount ratio ($2.15/day)</t>
+  </si>
+  <si>
+    <t>Regulatory Quality</t>
+  </si>
+  <si>
+    <t>Rule of Law</t>
+  </si>
+  <si>
     <t>Tax revenue (% of GDP)</t>
   </si>
   <si>
+    <t>Total reserves (current US$)</t>
+  </si>
+  <si>
+    <t>Total reserves (months of imports)</t>
+  </si>
+  <si>
+    <t>Trade openness (% of GDP)</t>
+  </si>
+  <si>
     <t>Unemployment (% labor force)</t>
+  </si>
+  <si>
+    <t>Urban population (% of total)</t>
+  </si>
+  <si>
+    <t>Voice and Accountability</t>
   </si>
   <si>
     <t>date</t>
@@ -389,12 +485,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:AL26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -411,493 +507,2683 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:38">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
-      <c r="B2">
+      <c r="E2">
+        <v>0.550269722938538</v>
+      </c>
+      <c r="F2">
+        <v>-0.125570459653347</v>
+      </c>
+      <c r="G2">
+        <v>39.6390583837328</v>
+      </c>
+      <c r="H2">
+        <v>117.095366481502</v>
+      </c>
+      <c r="I2">
+        <v>24.4043033106919</v>
+      </c>
+      <c r="J2">
+        <v>17.9488438094943</v>
+      </c>
+      <c r="K2">
+        <v>26668247021.2</v>
+      </c>
+      <c r="L2">
         <v>4.20000000067826</v>
       </c>
-      <c r="C2">
+      <c r="M2">
+        <v>8095.29428867929</v>
+      </c>
+      <c r="N2">
+        <v>3217.84693448467</v>
+      </c>
+      <c r="O2">
+        <v>3.25127058182207</v>
+      </c>
+      <c r="P2">
+        <v>57.8</v>
+      </c>
+      <c r="Q2">
+        <v>0.645909368991852</v>
+      </c>
+      <c r="R2">
+        <v>16.5672154108403</v>
+      </c>
+      <c r="S2">
+        <v>24.4358091522258</v>
+      </c>
+      <c r="T2">
+        <v>23.0698153754344</v>
+      </c>
+      <c r="U2">
+        <v>21.8164184247158</v>
+      </c>
+      <c r="V2">
         <v>5.33895913599827</v>
       </c>
-      <c r="D2">
+      <c r="W2">
         <v>18.1060049086277</v>
       </c>
-      <c r="E2">
+      <c r="X2">
+        <v>58.368</v>
+      </c>
+      <c r="Y2">
+        <v>1.38728913141799</v>
+      </c>
+      <c r="Z2">
+        <v>-1.71684047324677</v>
+      </c>
+      <c r="AA2">
+        <v>-0.227864950895309</v>
+      </c>
+      <c r="AB2">
+        <v>47159719</v>
+      </c>
+      <c r="AC2">
+        <v>47.9</v>
+      </c>
+      <c r="AD2">
+        <v>0.540943026542664</v>
+      </c>
+      <c r="AE2">
+        <v>0.148772299289703</v>
+      </c>
+      <c r="AF2">
         <v>20.9760632464162</v>
       </c>
-      <c r="F2">
+      <c r="AG2">
+        <v>7702061131.77162</v>
+      </c>
+      <c r="AH2">
+        <v>2.38388518393691</v>
+      </c>
+      <c r="AI2">
+        <v>46.2207217354077</v>
+      </c>
+      <c r="AJ2">
         <v>22.714</v>
       </c>
+      <c r="AK2">
+        <v>56.891</v>
+      </c>
+      <c r="AL2">
+        <v>0.746240437030792</v>
+      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:38">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3">
+      <c r="C3">
+        <v>3.77957571344558</v>
+      </c>
+      <c r="F3">
+        <v>0.253001084795547</v>
+      </c>
+      <c r="H3">
+        <v>121.069745626228</v>
+      </c>
+      <c r="I3">
+        <v>26.3566606345688</v>
+      </c>
+      <c r="J3">
+        <v>19.5001299531834</v>
+      </c>
+      <c r="K3">
+        <v>25680208730.5</v>
+      </c>
+      <c r="L3">
         <v>2.70000000019104</v>
       </c>
-      <c r="C3">
+      <c r="M3">
+        <v>8428.316817075311</v>
+      </c>
+      <c r="N3">
+        <v>2847.15191945908</v>
+      </c>
+      <c r="O3">
+        <v>1.82108406092082</v>
+      </c>
+      <c r="R3">
+        <v>16.6218512164789</v>
+      </c>
+      <c r="S3">
+        <v>24.3412920517984</v>
+      </c>
+      <c r="T3">
+        <v>24.0019951706408</v>
+      </c>
+      <c r="U3">
+        <v>22.8142845512603</v>
+      </c>
+      <c r="V3">
         <v>5.70189483049609</v>
       </c>
-      <c r="D3">
+      <c r="W3">
         <v>16.8016772079421</v>
       </c>
-      <c r="E3">
+      <c r="X3">
+        <v>57.161</v>
+      </c>
+      <c r="Y3">
+        <v>1.48316101798605</v>
+      </c>
+      <c r="Z3">
+        <v>-0.8019276640098471</v>
+      </c>
+      <c r="AB3">
+        <v>47566800</v>
+      </c>
+      <c r="AF3">
         <v>21.7005914264295</v>
       </c>
-      <c r="F3">
+      <c r="AG3">
+        <v>7626856919.15025</v>
+      </c>
+      <c r="AH3">
+        <v>2.45317346788814</v>
+      </c>
+      <c r="AI3">
+        <v>49.170945185829</v>
+      </c>
+      <c r="AJ3">
         <v>22.605</v>
       </c>
+      <c r="AK3">
+        <v>57.368</v>
+      </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:38">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
-      <c r="B4">
+      <c r="C4">
+        <v>9.653452618842771</v>
+      </c>
+      <c r="E4">
+        <v>0.332901507616043</v>
+      </c>
+      <c r="F4">
+        <v>0.781937464700479</v>
+      </c>
+      <c r="H4">
+        <v>97.3173728340893</v>
+      </c>
+      <c r="I4">
+        <v>28.4311672176802</v>
+      </c>
+      <c r="J4">
+        <v>27.7913348185499</v>
+      </c>
+      <c r="K4">
+        <v>35100005788.3</v>
+      </c>
+      <c r="L4">
         <v>3.70037440406668</v>
       </c>
-      <c r="C4">
+      <c r="M4">
+        <v>8792.355885742651</v>
+      </c>
+      <c r="N4">
+        <v>2688.23676032806</v>
+      </c>
+      <c r="O4">
+        <v>2.72292924025332</v>
+      </c>
+      <c r="Q4">
+        <v>0.607831418514252</v>
+      </c>
+      <c r="R4">
+        <v>16.7803880295906</v>
+      </c>
+      <c r="S4">
+        <v>23.6803783151852</v>
+      </c>
+      <c r="T4">
+        <v>22.7016759682254</v>
+      </c>
+      <c r="U4">
+        <v>25.0343344117566</v>
+      </c>
+      <c r="V4">
         <v>9.494713780995999</v>
       </c>
-      <c r="D4">
+      <c r="W4">
         <v>14.5583370058408</v>
       </c>
-      <c r="E4">
+      <c r="X4">
+        <v>55.58</v>
+      </c>
+      <c r="Y4">
+        <v>1.52930955872386</v>
+      </c>
+      <c r="Z4">
+        <v>-1.39209881025107</v>
+      </c>
+      <c r="AA4">
+        <v>-0.254789859056473</v>
+      </c>
+      <c r="AB4">
+        <v>48019415</v>
+      </c>
+      <c r="AD4">
+        <v>0.733767986297607</v>
+      </c>
+      <c r="AE4">
+        <v>0.0273917205631733</v>
+      </c>
+      <c r="AF4">
         <v>20.8248927712355</v>
       </c>
-      <c r="F4">
+      <c r="AG4">
+        <v>7816784858.41019</v>
+      </c>
+      <c r="AH4">
+        <v>2.50168882524225</v>
+      </c>
+      <c r="AI4">
+        <v>53.4655016294369</v>
+      </c>
+      <c r="AJ4">
         <v>22.547</v>
       </c>
+      <c r="AK4">
+        <v>57.898</v>
+      </c>
+      <c r="AL4">
+        <v>0.659822225570679</v>
+      </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:38">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
-      <c r="B5">
+      <c r="C5">
+        <v>3.74017326132098</v>
+      </c>
+      <c r="E5">
+        <v>0.275540828704834</v>
+      </c>
+      <c r="F5">
+        <v>-0.782449992267883</v>
+      </c>
+      <c r="H5">
+        <v>102.767701183828</v>
+      </c>
+      <c r="I5">
+        <v>23.9152733614034</v>
+      </c>
+      <c r="J5">
+        <v>20.8473533430208</v>
+      </c>
+      <c r="K5">
+        <v>40112300679.1</v>
+      </c>
+      <c r="L5">
         <v>2.94907546754213</v>
       </c>
-      <c r="C5">
+      <c r="M5">
+        <v>9138.82823855017</v>
+      </c>
+      <c r="N5">
+        <v>4062.21755993786</v>
+      </c>
+      <c r="O5">
+        <v>1.92822490144245</v>
+      </c>
+      <c r="Q5">
+        <v>0.599580049514771</v>
+      </c>
+      <c r="R5">
+        <v>16.8663209712168</v>
+      </c>
+      <c r="S5">
+        <v>24.7704671599849</v>
+      </c>
+      <c r="T5">
+        <v>22.7024907610567</v>
+      </c>
+      <c r="U5">
+        <v>21.8085892075755</v>
+      </c>
+      <c r="V5">
         <v>5.679424140688</v>
       </c>
-      <c r="D5">
+      <c r="W5">
         <v>12.5691941140716</v>
       </c>
-      <c r="E5">
+      <c r="X5">
+        <v>54.245</v>
+      </c>
+      <c r="Y5">
+        <v>1.4688112381823</v>
+      </c>
+      <c r="Z5">
+        <v>-2.26456368589691</v>
+      </c>
+      <c r="AA5">
+        <v>-0.312842577695847</v>
+      </c>
+      <c r="AB5">
+        <v>48500348</v>
+      </c>
+      <c r="AD5">
+        <v>0.819586336612701</v>
+      </c>
+      <c r="AE5">
+        <v>0.0375992655754089</v>
+      </c>
+      <c r="AF5">
         <v>20.4927670870354</v>
       </c>
-      <c r="F5">
+      <c r="AG5">
+        <v>8154089032.58033</v>
+      </c>
+      <c r="AH5">
+        <v>1.92764823872227</v>
+      </c>
+      <c r="AI5">
+        <v>45.723862568979</v>
+      </c>
+      <c r="AJ5">
         <v>22.629</v>
       </c>
+      <c r="AK5">
+        <v>58.446</v>
+      </c>
+      <c r="AL5">
+        <v>0.700217008590698</v>
+      </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:38">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
-      <c r="B6">
+      <c r="C6">
+        <v>3.66834602644474</v>
+      </c>
+      <c r="E6">
+        <v>0.397753119468689</v>
+      </c>
+      <c r="F6">
+        <v>-2.50726120703613</v>
+      </c>
+      <c r="H6">
+        <v>112.820913420211</v>
+      </c>
+      <c r="I6">
+        <v>22.7575187856654</v>
+      </c>
+      <c r="J6">
+        <v>17.499891670399</v>
+      </c>
+      <c r="K6">
+        <v>44011450239.9</v>
+      </c>
+      <c r="L6">
         <v>4.55455990721774</v>
       </c>
-      <c r="C6">
+      <c r="M6">
+        <v>9713.653484688341</v>
+      </c>
+      <c r="N6">
+        <v>5221.46333731721</v>
+      </c>
+      <c r="O6">
+        <v>3.50654128784933</v>
+      </c>
+      <c r="Q6">
+        <v>0.559140086174011</v>
+      </c>
+      <c r="R6">
+        <v>17.0044389815087</v>
+      </c>
+      <c r="S6">
+        <v>25.6020497773113</v>
+      </c>
+      <c r="T6">
+        <v>24.0807788202014</v>
+      </c>
+      <c r="U6">
+        <v>22.8860564383387</v>
+      </c>
+      <c r="V6">
         <v>-0.692039437857689</v>
       </c>
-      <c r="D6">
+      <c r="W6">
         <v>11.5613262515453</v>
       </c>
-      <c r="E6">
+      <c r="X6">
+        <v>53.963</v>
+      </c>
+      <c r="Y6">
+        <v>1.35572857797827</v>
+      </c>
+      <c r="Z6">
+        <v>-1.68236664045094</v>
+      </c>
+      <c r="AA6">
+        <v>-0.131729558110237</v>
+      </c>
+      <c r="AB6">
+        <v>48991421</v>
+      </c>
+      <c r="AD6">
+        <v>0.692467272281647</v>
+      </c>
+      <c r="AE6">
+        <v>0.00451626582071185</v>
+      </c>
+      <c r="AF6">
         <v>21.6985960707513</v>
       </c>
-      <c r="F6">
+      <c r="AG6">
+        <v>14886243628.1943</v>
+      </c>
+      <c r="AH6">
+        <v>2.68935775221081</v>
+      </c>
+      <c r="AI6">
+        <v>45.6435752240041</v>
+      </c>
+      <c r="AJ6">
         <v>22.538</v>
       </c>
+      <c r="AK6">
+        <v>58.993</v>
+      </c>
+      <c r="AL6">
+        <v>0.715736925601959</v>
+      </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:38">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
-      <c r="B7">
+      <c r="C7">
+        <v>3.27815389515675</v>
+      </c>
+      <c r="E7">
+        <v>0.483857184648514</v>
+      </c>
+      <c r="F7">
+        <v>-2.7747758989594</v>
+      </c>
+      <c r="H7">
+        <v>122.283168033262</v>
+      </c>
+      <c r="I7">
+        <v>23.5997644915436</v>
+      </c>
+      <c r="J7">
+        <v>15.8817076026059</v>
+      </c>
+      <c r="K7">
+        <v>45092242706.5</v>
+      </c>
+      <c r="L7">
         <v>5.27705197295467</v>
       </c>
-      <c r="C7">
+      <c r="M7">
+        <v>10440.6275147132</v>
+      </c>
+      <c r="N7">
+        <v>5836.87663325127</v>
+      </c>
+      <c r="O7">
+        <v>4.21638584977106</v>
+      </c>
+      <c r="P7">
+        <v>64.8</v>
+      </c>
+      <c r="Q7">
+        <v>0.567057847976685</v>
+      </c>
+      <c r="R7">
+        <v>16.1488985315911</v>
+      </c>
+      <c r="S7">
+        <v>25.6017227017192</v>
+      </c>
+      <c r="T7">
+        <v>25.7301385005501</v>
+      </c>
+      <c r="U7">
+        <v>23.8280169054893</v>
+      </c>
+      <c r="V7">
         <v>2.06285308223427</v>
       </c>
-      <c r="D7">
+      <c r="W7">
         <v>10.8593590528679</v>
       </c>
-      <c r="E7">
+      <c r="X7">
+        <v>53.914</v>
+      </c>
+      <c r="Y7">
+        <v>1.23481125272958</v>
+      </c>
+      <c r="Z7">
+        <v>-0.161839834643574</v>
+      </c>
+      <c r="AA7">
+        <v>-0.162092119455338</v>
+      </c>
+      <c r="AB7">
+        <v>49490033</v>
+      </c>
+      <c r="AC7">
+        <v>42.1</v>
+      </c>
+      <c r="AD7">
+        <v>0.715097188949585</v>
+      </c>
+      <c r="AE7">
+        <v>-0.0119512537494302</v>
+      </c>
+      <c r="AF7">
         <v>22.9721111805983</v>
       </c>
-      <c r="F7">
+      <c r="AG7">
+        <v>20624460695.2026</v>
+      </c>
+      <c r="AH7">
+        <v>3.16114379578521</v>
+      </c>
+      <c r="AI7">
+        <v>47.4277813970329</v>
+      </c>
+      <c r="AJ7">
         <v>22.461</v>
       </c>
+      <c r="AK7">
+        <v>59.536</v>
+      </c>
+      <c r="AL7">
+        <v>0.6490103602409359</v>
+      </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:38">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
-      <c r="B8">
+      <c r="C8">
+        <v>3.01715307976328</v>
+      </c>
+      <c r="E8">
+        <v>0.37827143073082</v>
+      </c>
+      <c r="F8">
+        <v>-4.00012427594728</v>
+      </c>
+      <c r="H8">
+        <v>139.007367744321</v>
+      </c>
+      <c r="I8">
+        <v>26.098249881712</v>
+      </c>
+      <c r="J8">
+        <v>19.3968431263798</v>
+      </c>
+      <c r="K8">
+        <v>57942874011.2</v>
+      </c>
+      <c r="L8">
         <v>5.60380645895889</v>
       </c>
-      <c r="C8">
+      <c r="M8">
+        <v>11250.179555872</v>
+      </c>
+      <c r="N8">
+        <v>6077.38293388876</v>
+      </c>
+      <c r="O8">
+        <v>4.53031944639788</v>
+      </c>
+      <c r="Q8">
+        <v>0.325101375579834</v>
+      </c>
+      <c r="R8">
+        <v>15.8607403931821</v>
+      </c>
+      <c r="S8">
+        <v>25.8417852811827</v>
+      </c>
+      <c r="T8">
+        <v>26.9292690601181</v>
+      </c>
+      <c r="U8">
+        <v>27.6698913924026</v>
+      </c>
+      <c r="V8">
         <v>3.24390765419229</v>
       </c>
-      <c r="D8">
+      <c r="W8">
         <v>9.850315674256519</v>
       </c>
-      <c r="E8">
+      <c r="X8">
+        <v>54.22</v>
+      </c>
+      <c r="Y8">
+        <v>1.15387200554978</v>
+      </c>
+      <c r="Z8">
+        <v>0.781786917588248</v>
+      </c>
+      <c r="AA8">
+        <v>0.0470300763845444</v>
+      </c>
+      <c r="AB8">
+        <v>49998277</v>
+      </c>
+      <c r="AD8">
+        <v>0.746972680091858</v>
+      </c>
+      <c r="AE8">
+        <v>0.181309819221497</v>
+      </c>
+      <c r="AF8">
         <v>24.3780853808343</v>
       </c>
-      <c r="F8">
+      <c r="AG8">
+        <v>25593361431.1639</v>
+      </c>
+      <c r="AH8">
+        <v>3.23727857447778</v>
+      </c>
+      <c r="AI8">
+        <v>53.7681412741145</v>
+      </c>
+      <c r="AJ8">
         <v>22.324</v>
       </c>
+      <c r="AK8">
+        <v>60.077</v>
+      </c>
+      <c r="AL8">
+        <v>0.651613116264343</v>
+      </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:38">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
-      <c r="B9">
+      <c r="C9">
+        <v>3.3798780439926</v>
+      </c>
+      <c r="E9">
+        <v>0.197672486305237</v>
+      </c>
+      <c r="F9">
+        <v>-4.86189160706926</v>
+      </c>
+      <c r="H9">
+        <v>142.422045511185</v>
+      </c>
+      <c r="I9">
+        <v>27.958964394702</v>
+      </c>
+      <c r="J9">
+        <v>22.519077312783</v>
+      </c>
+      <c r="K9">
+        <v>72806266042.2</v>
+      </c>
+      <c r="L9">
         <v>5.36047405394162</v>
       </c>
-      <c r="C9">
+      <c r="M9">
+        <v>12046.6051072501</v>
+      </c>
+      <c r="N9">
+        <v>6591.85535960564</v>
+      </c>
+      <c r="O9">
+        <v>4.25469604690063</v>
+      </c>
+      <c r="Q9">
+        <v>0.283431172370911</v>
+      </c>
+      <c r="R9">
+        <v>15.8864978575358</v>
+      </c>
+      <c r="S9">
+        <v>26.0805418540207</v>
+      </c>
+      <c r="T9">
+        <v>27.2583059687972</v>
+      </c>
+      <c r="U9">
+        <v>29.166174743045</v>
+      </c>
+      <c r="V9">
         <v>6.17781214809388</v>
       </c>
-      <c r="D9">
+      <c r="W9">
         <v>8.673096750264291</v>
       </c>
-      <c r="E9">
+      <c r="X9">
+        <v>54.948</v>
+      </c>
+      <c r="Y9">
+        <v>1.05851963686616</v>
+      </c>
+      <c r="Z9">
+        <v>0.924679916294093</v>
+      </c>
+      <c r="AA9">
+        <v>0.215346544981003</v>
+      </c>
+      <c r="AB9">
+        <v>50528584</v>
+      </c>
+      <c r="AD9">
+        <v>0.595666348934174</v>
+      </c>
+      <c r="AE9">
+        <v>0.000255581398960203</v>
+      </c>
+      <c r="AF9">
         <v>24.8072372824336</v>
       </c>
-      <c r="F9">
+      <c r="AG9">
+        <v>32919403650.564</v>
+      </c>
+      <c r="AH9">
+        <v>3.46397510382695</v>
+      </c>
+      <c r="AI9">
+        <v>57.125139137747</v>
+      </c>
+      <c r="AJ9">
         <v>22.287</v>
       </c>
+      <c r="AK9">
+        <v>60.616</v>
+      </c>
+      <c r="AL9">
+        <v>0.578765213489532</v>
+      </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:38">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
       <c r="B10">
+        <v>5.45350630049101</v>
+      </c>
+      <c r="C10">
+        <v>3.34620180721968</v>
+      </c>
+      <c r="D10">
+        <v>3.92151508288564</v>
+      </c>
+      <c r="E10">
+        <v>0.153828725218773</v>
+      </c>
+      <c r="F10">
+        <v>-5.1861810846768</v>
+      </c>
+      <c r="H10">
+        <v>125.955880255506</v>
+      </c>
+      <c r="I10">
+        <v>32.2546736710677</v>
+      </c>
+      <c r="J10">
+        <v>24.1786295037814</v>
+      </c>
+      <c r="K10">
+        <v>74274060700.8</v>
+      </c>
+      <c r="L10">
         <v>3.1910438863288</v>
       </c>
-      <c r="C10">
+      <c r="M10">
+        <v>12525.2630299811</v>
+      </c>
+      <c r="N10">
+        <v>6184.75474328399</v>
+      </c>
+      <c r="O10">
+        <v>2.00798658438173</v>
+      </c>
+      <c r="P10">
+        <v>63</v>
+      </c>
+      <c r="Q10">
+        <v>0.332178503274918</v>
+      </c>
+      <c r="R10">
+        <v>17.0724538163321</v>
+      </c>
+      <c r="S10">
+        <v>27.1771183464084</v>
+      </c>
+      <c r="T10">
+        <v>26.8712941110509</v>
+      </c>
+      <c r="U10">
+        <v>33.7198501285556</v>
+      </c>
+      <c r="V10">
         <v>9.909984560054671</v>
       </c>
-      <c r="D10">
+      <c r="W10">
         <v>7.6976073804606</v>
       </c>
-      <c r="E10">
+      <c r="X10">
+        <v>55.982</v>
+      </c>
+      <c r="Y10">
+        <v>1.03941759302272</v>
+      </c>
+      <c r="Z10">
+        <v>-0.5890955128302749</v>
+      </c>
+      <c r="AA10">
+        <v>0.049528993666172</v>
+      </c>
+      <c r="AB10">
+        <v>51114599</v>
+      </c>
+      <c r="AC10">
+        <v>30.3</v>
+      </c>
+      <c r="AD10">
+        <v>0.6569672226905821</v>
+      </c>
+      <c r="AE10">
+        <v>0.00541776139289141</v>
+      </c>
+      <c r="AF10">
         <v>24.322809870073</v>
       </c>
-      <c r="F10">
+      <c r="AG10">
+        <v>34070371606.9593</v>
+      </c>
+      <c r="AH10">
+        <v>3.3280835307273</v>
+      </c>
+      <c r="AI10">
+        <v>65.9745237996233</v>
+      </c>
+      <c r="AJ10">
         <v>22.407</v>
       </c>
+      <c r="AK10">
+        <v>61.154</v>
+      </c>
+      <c r="AL10">
+        <v>0.575648128986359</v>
+      </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:38">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
       <c r="B11">
+        <v>6.23096466231012</v>
+      </c>
+      <c r="C11">
+        <v>3.50229856382467</v>
+      </c>
+      <c r="D11">
+        <v>5.93611112398252</v>
+      </c>
+      <c r="E11">
+        <v>0.125426694750786</v>
+      </c>
+      <c r="F11">
+        <v>-2.38458187361532</v>
+      </c>
+      <c r="H11">
+        <v>121.094546324717</v>
+      </c>
+      <c r="I11">
+        <v>24.9827464883237</v>
+      </c>
+      <c r="J11">
+        <v>26.112601001907</v>
+      </c>
+      <c r="K11">
+        <v>84376757970</v>
+      </c>
+      <c r="L11">
         <v>-1.53808913525583</v>
       </c>
-      <c r="C11">
+      <c r="M11">
+        <v>12261.4115911303</v>
+      </c>
+      <c r="N11">
+        <v>6374.70560042992</v>
+      </c>
+      <c r="O11">
+        <v>-2.70664075062311</v>
+      </c>
+      <c r="Q11">
+        <v>0.310807675123215</v>
+      </c>
+      <c r="R11">
+        <v>17.7936331368919</v>
+      </c>
+      <c r="S11">
+        <v>29.1019033706759</v>
+      </c>
+      <c r="T11">
+        <v>24.9965390873939</v>
+      </c>
+      <c r="U11">
+        <v>24.6047888395564</v>
+      </c>
+      <c r="V11">
         <v>7.23809523809527</v>
       </c>
-      <c r="D11">
+      <c r="W11">
         <v>7.31227235926203</v>
       </c>
-      <c r="E11">
+      <c r="X11">
+        <v>57.413</v>
+      </c>
+      <c r="Y11">
+        <v>1.08950470906387</v>
+      </c>
+      <c r="Z11">
+        <v>-4.46450848490938</v>
+      </c>
+      <c r="AA11">
+        <v>-0.114492610096931</v>
+      </c>
+      <c r="AB11">
+        <v>51728516</v>
+      </c>
+      <c r="AD11">
+        <v>0.449182033538818</v>
+      </c>
+      <c r="AE11">
+        <v>0.07242307066917419</v>
+      </c>
+      <c r="AF11">
         <v>21.8948743006162</v>
       </c>
-      <c r="F11">
+      <c r="AG11">
+        <v>39602644576.4755</v>
+      </c>
+      <c r="AH11">
+        <v>5.12662348081341</v>
+      </c>
+      <c r="AI11">
+        <v>49.5875353278801</v>
+      </c>
+      <c r="AJ11">
         <v>23.523</v>
       </c>
+      <c r="AK11">
+        <v>61.687</v>
+      </c>
+      <c r="AL11">
+        <v>0.570525586605072</v>
+      </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:38">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
       <c r="B12">
+        <v>6.78389119750208</v>
+      </c>
+      <c r="C12">
+        <v>3.93474127187879</v>
+      </c>
+      <c r="D12">
+        <v>5.79213600421705</v>
+      </c>
+      <c r="E12">
+        <v>0.06539309769868849</v>
+      </c>
+      <c r="F12">
+        <v>-1.29901805615596</v>
+      </c>
+      <c r="H12">
+        <v>124.093899905646</v>
+      </c>
+      <c r="I12">
+        <v>25.7834176267221</v>
+      </c>
+      <c r="J12">
+        <v>28.1800559318895</v>
+      </c>
+      <c r="K12">
+        <v>115321955835.8</v>
+      </c>
+      <c r="L12">
         <v>3.03973288127956</v>
       </c>
-      <c r="C12">
+      <c r="M12">
+        <v>12637.2912226018</v>
+      </c>
+      <c r="N12">
+        <v>7973.47195771517</v>
+      </c>
+      <c r="O12">
+        <v>1.82804672464107</v>
+      </c>
+      <c r="P12">
+        <v>63.4</v>
+      </c>
+      <c r="Q12">
+        <v>0.191702410578728</v>
+      </c>
+      <c r="R12">
+        <v>17.996063602882</v>
+      </c>
+      <c r="S12">
+        <v>29.5775128260769</v>
+      </c>
+      <c r="T12">
+        <v>25.5192267165858</v>
+      </c>
+      <c r="U12">
+        <v>24.6226695358778</v>
+      </c>
+      <c r="V12">
         <v>4.06749555950264</v>
       </c>
-      <c r="D12">
+      <c r="W12">
         <v>7.68019097019604</v>
       </c>
-      <c r="E12">
+      <c r="X12">
+        <v>58.886</v>
+      </c>
+      <c r="Y12">
+        <v>1.00348106887351</v>
+      </c>
+      <c r="Z12">
+        <v>-4.44267265987095</v>
+      </c>
+      <c r="AA12">
+        <v>-0.0294270031154156</v>
+      </c>
+      <c r="AB12">
+        <v>52344051</v>
+      </c>
+      <c r="AC12">
+        <v>29.5</v>
+      </c>
+      <c r="AD12">
+        <v>0.445573270320892</v>
+      </c>
+      <c r="AE12">
+        <v>0.0977494567632675</v>
+      </c>
+      <c r="AF12">
         <v>22.5206038776132</v>
       </c>
-      <c r="F12">
+      <c r="AG12">
+        <v>43819545749.0238</v>
+      </c>
+      <c r="AH12">
+        <v>4.54059848802417</v>
+      </c>
+      <c r="AI12">
+        <v>50.4060871625999</v>
+      </c>
+      <c r="AJ12">
         <v>24.683</v>
       </c>
+      <c r="AK12">
+        <v>62.218</v>
+      </c>
+      <c r="AL12">
+        <v>0.602090120315552</v>
+      </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:38">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
       <c r="B13">
+        <v>6.83583959729123</v>
+      </c>
+      <c r="C13">
+        <v>3.98109763512117</v>
+      </c>
+      <c r="D13">
+        <v>4.68085453063316</v>
+      </c>
+      <c r="E13">
+        <v>-0.00423370534554124</v>
+      </c>
+      <c r="F13">
+        <v>-2.01967628513274</v>
+      </c>
+      <c r="H13">
+        <v>118.970675992703</v>
+      </c>
+      <c r="I13">
+        <v>27.6981484703752</v>
+      </c>
+      <c r="J13">
+        <v>27.7414231921247</v>
+      </c>
+      <c r="K13">
+        <v>124137231364.7</v>
+      </c>
+      <c r="L13">
         <v>3.16855627858818</v>
       </c>
-      <c r="C13">
+      <c r="M13">
+        <v>13143.1933361097</v>
+      </c>
+      <c r="N13">
+        <v>8646.055710716349</v>
+      </c>
+      <c r="O13">
+        <v>1.90092049729387</v>
+      </c>
+      <c r="Q13">
+        <v>0.217559650540352</v>
+      </c>
+      <c r="R13">
+        <v>18.1951431854763</v>
+      </c>
+      <c r="S13">
+        <v>31.0619734464171</v>
+      </c>
+      <c r="T13">
+        <v>25.9740547550987</v>
+      </c>
+      <c r="U13">
+        <v>26.9382019655219</v>
+      </c>
+      <c r="V13">
         <v>5.00085338795019</v>
       </c>
-      <c r="D13">
+      <c r="W13">
         <v>7.90376276286169</v>
       </c>
-      <c r="E13">
+      <c r="X13">
+        <v>60.602</v>
+      </c>
+      <c r="Y13">
+        <v>1.00265340405471</v>
+      </c>
+      <c r="Z13">
+        <v>-5.46206329752573</v>
+      </c>
+      <c r="AA13">
+        <v>0.0240315701812506</v>
+      </c>
+      <c r="AB13">
+        <v>52995205</v>
+      </c>
+      <c r="AD13">
+        <v>0.446406275033951</v>
+      </c>
+      <c r="AE13">
+        <v>0.129662588238716</v>
+      </c>
+      <c r="AF13">
         <v>22.8746700116825</v>
       </c>
-      <c r="F13">
+      <c r="AG13">
+        <v>48748260246.0381</v>
+      </c>
+      <c r="AH13">
+        <v>4.19180307031225</v>
+      </c>
+      <c r="AI13">
+        <v>54.6363504358971</v>
+      </c>
+      <c r="AJ13">
         <v>24.639</v>
       </c>
+      <c r="AK13">
+        <v>62.746</v>
+      </c>
+      <c r="AL13">
+        <v>0.590838611125946</v>
+      </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:38">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
       <c r="B14">
+        <v>7.4369887255935</v>
+      </c>
+      <c r="C14">
+        <v>3.5268307442793</v>
+      </c>
+      <c r="D14">
+        <v>4.04289177410579</v>
+      </c>
+      <c r="E14">
+        <v>-0.184170603752136</v>
+      </c>
+      <c r="F14">
+        <v>-4.68373643403848</v>
+      </c>
+      <c r="H14">
+        <v>125.167785450237</v>
+      </c>
+      <c r="I14">
+        <v>27.1391491937679</v>
+      </c>
+      <c r="J14">
+        <v>34.9360348114713</v>
+      </c>
+      <c r="K14">
+        <v>147959953649.6</v>
+      </c>
+      <c r="L14">
         <v>2.39623238465745</v>
       </c>
-      <c r="C14">
+      <c r="M14">
+        <v>12986.7976675307</v>
+      </c>
+      <c r="N14">
+        <v>8076.97678479741</v>
+      </c>
+      <c r="O14">
+        <v>0.897179683754416</v>
+      </c>
+      <c r="Q14">
+        <v>0.170115306973457</v>
+      </c>
+      <c r="R14">
+        <v>18.8205452606488</v>
+      </c>
+      <c r="S14">
+        <v>30.3651797341743</v>
+      </c>
+      <c r="T14">
+        <v>26.5227856834625</v>
+      </c>
+      <c r="U14">
+        <v>28.4434679995666</v>
+      </c>
+      <c r="V14">
         <v>5.73797139141737</v>
       </c>
-      <c r="D14">
+      <c r="W14">
         <v>8.7038710886434</v>
       </c>
-      <c r="E14">
+      <c r="X14">
+        <v>61.737</v>
+      </c>
+      <c r="Y14">
+        <v>1.03352274081458</v>
+      </c>
+      <c r="Z14">
+        <v>-4.23209308673638</v>
+      </c>
+      <c r="AA14">
+        <v>-0.0253867004066706</v>
+      </c>
+      <c r="AB14">
+        <v>53782567</v>
+      </c>
+      <c r="AD14">
+        <v>0.398661673069</v>
+      </c>
+      <c r="AE14">
+        <v>0.08444415777921679</v>
+      </c>
+      <c r="AF14">
         <v>23.3457659894736</v>
       </c>
-      <c r="F14">
+      <c r="AG14">
+        <v>50688078405.0297</v>
+      </c>
+      <c r="AH14">
+        <v>4.33171873217314</v>
+      </c>
+      <c r="AI14">
+        <v>55.5826171933345</v>
+      </c>
+      <c r="AJ14">
         <v>24.727</v>
       </c>
+      <c r="AK14">
+        <v>63.272</v>
+      </c>
+      <c r="AL14">
+        <v>0.5821533203125</v>
+      </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:38">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
       <c r="B15">
+        <v>7.55530675097008</v>
+      </c>
+      <c r="C15">
+        <v>3.54018854420615</v>
+      </c>
+      <c r="D15">
+        <v>3.64128702921644</v>
+      </c>
+      <c r="E15">
+        <v>-0.138074696063995</v>
+      </c>
+      <c r="F15">
+        <v>-5.33837274756911</v>
+      </c>
+      <c r="H15">
+        <v>127.029272479725</v>
+      </c>
+      <c r="I15">
+        <v>28.379280320361</v>
+      </c>
+      <c r="J15">
+        <v>36.2068137000957</v>
+      </c>
+      <c r="K15">
+        <v>141639140528.1</v>
+      </c>
+      <c r="L15">
         <v>2.48546800826588</v>
       </c>
-      <c r="C15">
+      <c r="M15">
+        <v>13369.4382039605</v>
+      </c>
+      <c r="N15">
+        <v>7331.65467384919</v>
+      </c>
+      <c r="O15">
+        <v>0.805658809846705</v>
+      </c>
+      <c r="Q15">
+        <v>0.30602103471756</v>
+      </c>
+      <c r="R15">
+        <v>19.0813745546722</v>
+      </c>
+      <c r="S15">
+        <v>31.259190573785</v>
+      </c>
+      <c r="T15">
+        <v>27.4101862231804</v>
+      </c>
+      <c r="U15">
+        <v>30.4957473096901</v>
+      </c>
+      <c r="V15">
         <v>5.78016910069177</v>
       </c>
-      <c r="D15">
+      <c r="W15">
         <v>8.737755337317539</v>
       </c>
-      <c r="E15">
+      <c r="X15">
+        <v>62.388</v>
+      </c>
+      <c r="Y15">
+        <v>1.02779402383821</v>
+      </c>
+      <c r="Z15">
+        <v>-4.18299310803963</v>
+      </c>
+      <c r="AA15">
+        <v>-0.0462945364415646</v>
+      </c>
+      <c r="AB15">
+        <v>54678791</v>
+      </c>
+      <c r="AD15">
+        <v>0.380482465028763</v>
+      </c>
+      <c r="AE15">
+        <v>0.135300785303116</v>
+      </c>
+      <c r="AF15">
         <v>23.831391363238</v>
       </c>
-      <c r="F15">
+      <c r="AG15">
+        <v>49708174893.5691</v>
+      </c>
+      <c r="AH15">
+        <v>4.30463726127469</v>
+      </c>
+      <c r="AI15">
+        <v>58.875027630051</v>
+      </c>
+      <c r="AJ15">
         <v>24.561</v>
       </c>
+      <c r="AK15">
+        <v>63.793</v>
+      </c>
+      <c r="AL15">
+        <v>0.600654542446136</v>
+      </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:38">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
       <c r="B16">
+        <v>7.16761401120425</v>
+      </c>
+      <c r="C16">
+        <v>3.45306169950531</v>
+      </c>
+      <c r="D16">
+        <v>3.24484679094119</v>
+      </c>
+      <c r="E16">
+        <v>-0.125287011265755</v>
+      </c>
+      <c r="F16">
+        <v>-4.81243259488483</v>
+      </c>
+      <c r="H16">
+        <v>128.838374779653</v>
+      </c>
+      <c r="I16">
+        <v>29.0006193033471</v>
+      </c>
+      <c r="J16">
+        <v>40.1667158742941</v>
+      </c>
+      <c r="K16">
+        <v>149317852206.3</v>
+      </c>
+      <c r="L16">
         <v>1.41382645223793</v>
       </c>
-      <c r="C16">
+      <c r="M16">
+        <v>13358.9417186608</v>
+      </c>
+      <c r="N16">
+        <v>6856.73137092522</v>
+      </c>
+      <c r="O16">
+        <v>-0.257188966137676</v>
+      </c>
+      <c r="P16">
+        <v>63</v>
+      </c>
+      <c r="Q16">
+        <v>0.165043815970421</v>
+      </c>
+      <c r="R16">
+        <v>19.3140625940978</v>
+      </c>
+      <c r="S16">
+        <v>31.9053501556958</v>
+      </c>
+      <c r="T16">
+        <v>28.8726130567165</v>
+      </c>
+      <c r="U16">
+        <v>30.4989547517121</v>
+      </c>
+      <c r="V16">
         <v>6.13282953059149</v>
       </c>
-      <c r="D16">
+      <c r="W16">
         <v>9.179413341109409</v>
       </c>
-      <c r="E16">
+      <c r="X16">
+        <v>63.184</v>
+      </c>
+      <c r="Y16">
+        <v>1.02189399625968</v>
+      </c>
+      <c r="Z16">
+        <v>-3.43956150956061</v>
+      </c>
+      <c r="AA16">
+        <v>-0.146388962864876</v>
+      </c>
+      <c r="AB16">
+        <v>55594838</v>
+      </c>
+      <c r="AC16">
+        <v>31.2</v>
+      </c>
+      <c r="AD16">
+        <v>0.230833724141121</v>
+      </c>
+      <c r="AE16">
+        <v>0.155199274420738</v>
+      </c>
+      <c r="AF16">
         <v>24.4319342176034</v>
       </c>
-      <c r="F16">
+      <c r="AG16">
+        <v>49121568380.4854</v>
+      </c>
+      <c r="AH16">
+        <v>4.42516066122754</v>
+      </c>
+      <c r="AI16">
+        <v>59.4995740550593</v>
+      </c>
+      <c r="AJ16">
         <v>24.89</v>
       </c>
+      <c r="AK16">
+        <v>64.312</v>
+      </c>
+      <c r="AL16">
+        <v>0.640296518802643</v>
+      </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:38">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
       <c r="B17">
+        <v>7.12183209283378</v>
+      </c>
+      <c r="C17">
+        <v>3.13847282974406</v>
+      </c>
+      <c r="D17">
+        <v>3.12168564309893</v>
+      </c>
+      <c r="E17">
+        <v>-0.0708397477865219</v>
+      </c>
+      <c r="F17">
+        <v>-4.31028688643788</v>
+      </c>
+      <c r="G17">
+        <v>52.6511572360833</v>
+      </c>
+      <c r="H17">
+        <v>127.203244242731</v>
+      </c>
+      <c r="I17">
+        <v>27.7136384124829</v>
+      </c>
+      <c r="J17">
+        <v>37.7078002750993</v>
+      </c>
+      <c r="K17">
+        <v>127741439982.3</v>
+      </c>
+      <c r="L17">
         <v>1.32186223678229</v>
       </c>
-      <c r="C17">
+      <c r="M17">
+        <v>13397.5234813346</v>
+      </c>
+      <c r="N17">
+        <v>6112.27382485974</v>
+      </c>
+      <c r="O17">
+        <v>-0.694265293924985</v>
+      </c>
+      <c r="Q17">
+        <v>0.0873290970921516</v>
+      </c>
+      <c r="R17">
+        <v>18.9850713286308</v>
+      </c>
+      <c r="S17">
+        <v>33.6797787454907</v>
+      </c>
+      <c r="T17">
+        <v>29.6472581887112</v>
+      </c>
+      <c r="U17">
+        <v>29.0130377322327</v>
+      </c>
+      <c r="V17">
         <v>4.5186909489251</v>
       </c>
-      <c r="D17">
+      <c r="W17">
         <v>9.098965099900539</v>
       </c>
-      <c r="E17">
+      <c r="X17">
+        <v>64.053</v>
+      </c>
+      <c r="Y17">
+        <v>1.00692862196088</v>
+      </c>
+      <c r="Z17">
+        <v>-4.56437663555894</v>
+      </c>
+      <c r="AA17">
+        <v>-0.220544874668121</v>
+      </c>
+      <c r="AB17">
+        <v>56723537</v>
+      </c>
+      <c r="AD17">
+        <v>0.208593904972076</v>
+      </c>
+      <c r="AE17">
+        <v>0.0157780386507511</v>
+      </c>
+      <c r="AF17">
         <v>25.0486927031144</v>
       </c>
-      <c r="F17">
+      <c r="AG17">
+        <v>45887065756.7249</v>
+      </c>
+      <c r="AH17">
+        <v>4.724214132513</v>
+      </c>
+      <c r="AI17">
+        <v>56.7266761447156</v>
+      </c>
+      <c r="AJ17">
         <v>25.149</v>
       </c>
+      <c r="AK17">
+        <v>64.828</v>
+      </c>
+      <c r="AL17">
+        <v>0.648553431034088</v>
+      </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:38">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
       <c r="B18">
+        <v>7.64707124159309</v>
+      </c>
+      <c r="C18">
+        <v>3.4988975508153</v>
+      </c>
+      <c r="D18">
+        <v>2.85780789685004</v>
+      </c>
+      <c r="E18">
+        <v>0.0170262884348631</v>
+      </c>
+      <c r="F18">
+        <v>-2.63361451678798</v>
+      </c>
+      <c r="G18">
+        <v>53.7387913884354</v>
+      </c>
+      <c r="H18">
+        <v>124.360496111764</v>
+      </c>
+      <c r="I18">
+        <v>28.1560881698955</v>
+      </c>
+      <c r="J18">
+        <v>45.6869077355498</v>
+      </c>
+      <c r="K18">
+        <v>144048128970.8</v>
+      </c>
+      <c r="L18">
         <v>0.664552307858116</v>
       </c>
-      <c r="C18">
+      <c r="M18">
+        <v>13519.3235102376</v>
+      </c>
+      <c r="N18">
+        <v>5651.20585165749</v>
+      </c>
+      <c r="O18">
+        <v>-0.277781475736276</v>
+      </c>
+      <c r="Q18">
+        <v>0.101402580738068</v>
+      </c>
+      <c r="R18">
+        <v>19.3075616545523</v>
+      </c>
+      <c r="S18">
+        <v>32.1896608002111</v>
+      </c>
+      <c r="T18">
+        <v>29.0406590015195</v>
+      </c>
+      <c r="U18">
+        <v>27.7051693349827</v>
+      </c>
+      <c r="V18">
         <v>6.60290842394869</v>
       </c>
-      <c r="D18">
+      <c r="W18">
         <v>10.2150196800716</v>
       </c>
-      <c r="E18">
+      <c r="X18">
+        <v>64.749</v>
+      </c>
+      <c r="Y18">
+        <v>0.971046764986093</v>
+      </c>
+      <c r="Z18">
+        <v>-3.46049874466043</v>
+      </c>
+      <c r="AA18">
+        <v>-0.149085000157356</v>
+      </c>
+      <c r="AB18">
+        <v>57259551</v>
+      </c>
+      <c r="AD18">
+        <v>0.119783155620098</v>
+      </c>
+      <c r="AE18">
+        <v>0.0435598641633987</v>
+      </c>
+      <c r="AF18">
         <v>24.8283559884696</v>
       </c>
-      <c r="F18">
+      <c r="AG18">
+        <v>47180127300.8565</v>
+      </c>
+      <c r="AH18">
+        <v>5.43700662124582</v>
+      </c>
+      <c r="AI18">
+        <v>55.8612575048782</v>
+      </c>
+      <c r="AJ18">
         <v>26.536</v>
       </c>
+      <c r="AK18">
+        <v>65.34099999999999</v>
+      </c>
+      <c r="AL18">
+        <v>0.648330509662628</v>
+      </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:38">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
       <c r="B19">
+        <v>8.19395489709604</v>
+      </c>
+      <c r="C19">
+        <v>3.46424605385381</v>
+      </c>
+      <c r="D19">
+        <v>2.84200004498428</v>
+      </c>
+      <c r="E19">
+        <v>-0.12777316570282</v>
+      </c>
+      <c r="F19">
+        <v>-2.37436753188649</v>
+      </c>
+      <c r="G19">
+        <v>56.2597208390879</v>
+      </c>
+      <c r="H19">
+        <v>127.030283858454</v>
+      </c>
+      <c r="I19">
+        <v>27.3400757812216</v>
+      </c>
+      <c r="J19">
+        <v>47.189634345937</v>
+      </c>
+      <c r="K19">
+        <v>175013606856.1</v>
+      </c>
+      <c r="L19">
         <v>1.15794695181735</v>
       </c>
-      <c r="C19">
+      <c r="M19">
+        <v>13738.4385854596</v>
+      </c>
+      <c r="N19">
+        <v>6618.33508255701</v>
+      </c>
+      <c r="O19">
+        <v>0.49869596172698</v>
+      </c>
+      <c r="Q19">
+        <v>0.07079592347145081</v>
+      </c>
+      <c r="R19">
+        <v>19.2360771279531</v>
+      </c>
+      <c r="S19">
+        <v>33.2518124768773</v>
+      </c>
+      <c r="T19">
+        <v>28.9131558196206</v>
+      </c>
+      <c r="U19">
+        <v>26.1958560481525</v>
+      </c>
+      <c r="V19">
         <v>5.18618655524146</v>
       </c>
-      <c r="D19">
+      <c r="W19">
         <v>10.5634519284442</v>
       </c>
-      <c r="E19">
+      <c r="X19">
+        <v>65.422</v>
+      </c>
+      <c r="Y19">
+        <v>0.943568494750462</v>
+      </c>
+      <c r="Z19">
+        <v>-4.65754447743392</v>
+      </c>
+      <c r="AA19">
+        <v>-0.284803628921509</v>
+      </c>
+      <c r="AB19">
+        <v>57635162</v>
+      </c>
+      <c r="AD19">
+        <v>0.13887757062912</v>
+      </c>
+      <c r="AE19">
+        <v>-0.15624788403511</v>
+      </c>
+      <c r="AF19">
         <v>24.76928728931</v>
       </c>
-      <c r="F19">
+      <c r="AG19">
+        <v>50722891363.2361</v>
+      </c>
+      <c r="AH19">
+        <v>5.2254571809234</v>
+      </c>
+      <c r="AI19">
+        <v>53.5359318293741</v>
+      </c>
+      <c r="AJ19">
         <v>27.035</v>
       </c>
+      <c r="AK19">
+        <v>65.84999999999999</v>
+      </c>
+      <c r="AL19">
+        <v>0.630274713039398</v>
+      </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:38">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
       <c r="B20">
+        <v>7.91208376467566</v>
+      </c>
+      <c r="C20">
+        <v>3.33065585318159</v>
+      </c>
+      <c r="D20">
+        <v>3.72802083553832</v>
+      </c>
+      <c r="E20">
+        <v>-0.136797428131104</v>
+      </c>
+      <c r="F20">
+        <v>-3.00051939426576</v>
+      </c>
+      <c r="G20">
+        <v>59.1023114070608</v>
+      </c>
+      <c r="H20">
+        <v>118.380857963487</v>
+      </c>
+      <c r="I20">
+        <v>27.4970371508423</v>
+      </c>
+      <c r="J20">
+        <v>45.7386176540485</v>
+      </c>
+      <c r="K20">
+        <v>180183961226</v>
+      </c>
+      <c r="L20">
         <v>1.55678384721676</v>
       </c>
-      <c r="C20">
+      <c r="M20">
+        <v>13347.3634826038</v>
+      </c>
+      <c r="N20">
+        <v>6914.1780318076</v>
+      </c>
+      <c r="O20">
+        <v>-0.1374850396532</v>
+      </c>
+      <c r="Q20">
+        <v>0.103647440671921</v>
+      </c>
+      <c r="R20">
+        <v>19.352226142463</v>
+      </c>
+      <c r="S20">
+        <v>33.9954978254972</v>
+      </c>
+      <c r="T20">
+        <v>28.3643368318902</v>
+      </c>
+      <c r="U20">
+        <v>26.9885079767917</v>
+      </c>
+      <c r="V20">
         <v>4.50987264867393</v>
       </c>
-      <c r="D20">
+      <c r="W20">
         <v>10.5625640407853</v>
       </c>
-      <c r="E20">
+      <c r="X20">
+        <v>65.726</v>
+      </c>
+      <c r="Y20">
+        <v>0.894757064750116</v>
+      </c>
+      <c r="Z20">
+        <v>-5.69551397247214</v>
+      </c>
+      <c r="AA20">
+        <v>-0.237546816468239</v>
+      </c>
+      <c r="AB20">
+        <v>58613001</v>
+      </c>
+      <c r="AD20">
+        <v>-0.0407781675457954</v>
+      </c>
+      <c r="AE20">
+        <v>-0.22182808816433</v>
+      </c>
+      <c r="AF20">
         <v>24.8948940727422</v>
       </c>
-      <c r="F20">
+      <c r="AG20">
+        <v>51642041966.6735</v>
+      </c>
+      <c r="AH20">
+        <v>4.81246249518313</v>
+      </c>
+      <c r="AI20">
+        <v>54.4855451276341</v>
+      </c>
+      <c r="AJ20">
         <v>26.906</v>
       </c>
+      <c r="AK20">
+        <v>66.355</v>
+      </c>
+      <c r="AL20">
+        <v>0.63723361492157</v>
+      </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:38">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
       <c r="B21">
+        <v>8.007959105109499</v>
+      </c>
+      <c r="C21">
+        <v>3.38605165058031</v>
+      </c>
+      <c r="D21">
+        <v>3.89239038176021</v>
+      </c>
+      <c r="E21">
+        <v>-0.0312809906899929</v>
+      </c>
+      <c r="F21">
+        <v>-2.6199906748304</v>
+      </c>
+      <c r="G21">
+        <v>64.5892781351104</v>
+      </c>
+      <c r="H21">
+        <v>117.185556861489</v>
+      </c>
+      <c r="I21">
+        <v>27.2021294051151</v>
+      </c>
+      <c r="J21">
+        <v>50.2455135053928</v>
+      </c>
+      <c r="K21">
+        <v>190737954551.6</v>
+      </c>
+      <c r="L21">
         <v>0.25993557687633</v>
       </c>
-      <c r="C21">
+      <c r="M21">
+        <v>13361.4851289112</v>
+      </c>
+      <c r="N21">
+        <v>6533.71121032856</v>
+      </c>
+      <c r="O21">
+        <v>-1.3803610544763</v>
+      </c>
+      <c r="Q21">
+        <v>0.127971157431602</v>
+      </c>
+      <c r="R21">
+        <v>19.5800800398681</v>
+      </c>
+      <c r="S21">
+        <v>34.6532754617872</v>
+      </c>
+      <c r="T21">
+        <v>28.8976157499402</v>
+      </c>
+      <c r="U21">
+        <v>26.6958670030255</v>
+      </c>
+      <c r="V21">
         <v>4.1028507546115</v>
       </c>
-      <c r="D21">
+      <c r="W21">
         <v>11.041411159621</v>
       </c>
-      <c r="E21">
+      <c r="X21">
+        <v>66.071</v>
+      </c>
+      <c r="Y21">
+        <v>0.882430271670915</v>
+      </c>
+      <c r="Z21">
+        <v>-5.75192703897</v>
+      </c>
+      <c r="AA21">
+        <v>-0.2832210958004</v>
+      </c>
+      <c r="AB21">
+        <v>59587885</v>
+      </c>
+      <c r="AD21">
+        <v>0.00850539095699787</v>
+      </c>
+      <c r="AE21">
+        <v>-0.188336730003357</v>
+      </c>
+      <c r="AF21">
         <v>24.8673453267976</v>
       </c>
-      <c r="F21">
+      <c r="AG21">
+        <v>55055893656.867</v>
+      </c>
+      <c r="AH21">
+        <v>5.40690081512174</v>
+      </c>
+      <c r="AI21">
+        <v>53.8979964081406</v>
+      </c>
+      <c r="AJ21">
         <v>28.468</v>
       </c>
+      <c r="AK21">
+        <v>66.85599999999999</v>
+      </c>
+      <c r="AL21">
+        <v>0.643925607204437</v>
+      </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:38">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
       <c r="B22">
+        <v>7.61014587740305</v>
+      </c>
+      <c r="C22">
+        <v>3.19703305521804</v>
+      </c>
+      <c r="D22">
+        <v>5.18028329482246</v>
+      </c>
+      <c r="E22">
+        <v>-0.0594757050275803</v>
+      </c>
+      <c r="F22">
+        <v>2.00352275153333</v>
+      </c>
+      <c r="G22">
+        <v>75.7255090793216</v>
+      </c>
+      <c r="H22">
+        <v>109.054691372725</v>
+      </c>
+      <c r="I22">
+        <v>27.5759141603963</v>
+      </c>
+      <c r="J22">
+        <v>52.780991413988</v>
+      </c>
+      <c r="K22">
+        <v>175416998140</v>
+      </c>
+      <c r="L22">
         <v>-6.1689177146757</v>
       </c>
-      <c r="C22">
+      <c r="M22">
+        <v>12671.0862436851</v>
+      </c>
+      <c r="N22">
+        <v>5580.60383075189</v>
+      </c>
+      <c r="O22">
+        <v>-7.67873309598839</v>
+      </c>
+      <c r="Q22">
+        <v>0.0465345233678818</v>
+      </c>
+      <c r="R22">
+        <v>20.6203398698938</v>
+      </c>
+      <c r="S22">
+        <v>37.8354162011745</v>
+      </c>
+      <c r="T22">
+        <v>27.8138753889078</v>
+      </c>
+      <c r="U22">
+        <v>23.1837449200214</v>
+      </c>
+      <c r="V22">
         <v>3.23238831615119</v>
       </c>
-      <c r="D22">
+      <c r="W22">
         <v>11.4297572612146</v>
       </c>
-      <c r="E22">
+      <c r="X22">
+        <v>65.15000000000001</v>
+      </c>
+      <c r="Y22">
+        <v>0.955615163117871</v>
+      </c>
+      <c r="Z22">
+        <v>-9.92664872393274</v>
+      </c>
+      <c r="AA22">
+        <v>-0.252867221832275</v>
+      </c>
+      <c r="AB22">
+        <v>60562381</v>
+      </c>
+      <c r="AD22">
+        <v>0.0204948224127293</v>
+      </c>
+      <c r="AE22">
+        <v>-0.243993982672691</v>
+      </c>
+      <c r="AF22">
         <v>23.2649440409195</v>
       </c>
-      <c r="F22">
+      <c r="AG22">
+        <v>55008491995.5568</v>
+      </c>
+      <c r="AH22">
+        <v>7.12354295570033</v>
+      </c>
+      <c r="AI22">
+        <v>50.7596590804177</v>
+      </c>
+      <c r="AJ22">
         <v>29.217</v>
       </c>
+      <c r="AK22">
+        <v>67.354</v>
+      </c>
+      <c r="AL22">
+        <v>0.690293967723846</v>
+      </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:38">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
       <c r="B23">
+        <v>8.09058344861373</v>
+      </c>
+      <c r="C23">
+        <v>3.31369006300886</v>
+      </c>
+      <c r="D23">
+        <v>4.45425562129511</v>
+      </c>
+      <c r="E23">
+        <v>-0.0341691114008427</v>
+      </c>
+      <c r="F23">
+        <v>3.76434166625779</v>
+      </c>
+      <c r="G23">
+        <v>73.8065091009354</v>
+      </c>
+      <c r="H23">
+        <v>92.99697264147321</v>
+      </c>
+      <c r="I23">
+        <v>31.1035988061883</v>
+      </c>
+      <c r="J23">
+        <v>41.0396501185489</v>
+      </c>
+      <c r="K23">
+        <v>169438160061.5</v>
+      </c>
+      <c r="L23">
         <v>4.95503259440756</v>
       </c>
-      <c r="C23">
+      <c r="M23">
+        <v>13711.2935730474</v>
+      </c>
+      <c r="N23">
+        <v>6843.39941886204</v>
+      </c>
+      <c r="O23">
+        <v>3.35053090110557</v>
+      </c>
+      <c r="Q23">
+        <v>-0.0701303705573082</v>
+      </c>
+      <c r="R23">
+        <v>19.1782663776178</v>
+      </c>
+      <c r="S23">
+        <v>34.53100888431</v>
+      </c>
+      <c r="T23">
+        <v>30.0652667080962</v>
+      </c>
+      <c r="U23">
+        <v>24.9311150310516</v>
+      </c>
+      <c r="V23">
         <v>4.61874544887136</v>
       </c>
-      <c r="D23">
+      <c r="W23">
         <v>12.92388692824</v>
       </c>
-      <c r="E23">
+      <c r="X23">
+        <v>62.01</v>
+      </c>
+      <c r="Y23">
+        <v>0.80744046915839</v>
+      </c>
+      <c r="Z23">
+        <v>-4.49568737459651</v>
+      </c>
+      <c r="AA23">
+        <v>-0.750981450080872</v>
+      </c>
+      <c r="AB23">
+        <v>61502603</v>
+      </c>
+      <c r="AD23">
+        <v>-0.09070863574743269</v>
+      </c>
+      <c r="AE23">
+        <v>0.06497969478368761</v>
+      </c>
+      <c r="AF23">
         <v>25.8946273252854</v>
       </c>
-      <c r="F23">
+      <c r="AG23">
+        <v>57597149617.2517</v>
+      </c>
+      <c r="AH23">
+        <v>5.56291275582496</v>
+      </c>
+      <c r="AI23">
+        <v>56.0347138372399</v>
+      </c>
+      <c r="AJ23">
         <v>34.007</v>
       </c>
+      <c r="AK23">
+        <v>67.84699999999999</v>
+      </c>
+      <c r="AL23">
+        <v>0.783295750617981</v>
+      </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:38">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
-      <c r="B24">
+      <c r="C24">
+        <v>3.88695734744765</v>
+      </c>
+      <c r="E24">
+        <v>-0.33009460568428</v>
+      </c>
+      <c r="F24">
+        <v>-0.296674662487372</v>
+      </c>
+      <c r="G24">
+        <v>76.2372383337531</v>
+      </c>
+      <c r="H24">
+        <v>91.721858565369</v>
+      </c>
+      <c r="I24">
+        <v>33.3714495540545</v>
+      </c>
+      <c r="J24">
+        <v>43.0974181830946</v>
+      </c>
+      <c r="K24">
+        <v>171723253547.3</v>
+      </c>
+      <c r="L24">
         <v>1.91147996033504</v>
       </c>
-      <c r="C24">
+      <c r="M24">
+        <v>14759.4350715619</v>
+      </c>
+      <c r="N24">
+        <v>6523.41097815853</v>
+      </c>
+      <c r="O24">
+        <v>0.480619707090057</v>
+      </c>
+      <c r="Q24">
+        <v>-0.109027646481991</v>
+      </c>
+      <c r="R24">
+        <v>18.9892702779701</v>
+      </c>
+      <c r="S24">
+        <v>33.4798352578178</v>
+      </c>
+      <c r="T24">
+        <v>30.273151278645</v>
+      </c>
+      <c r="U24">
+        <v>31.4115525789563</v>
+      </c>
+      <c r="V24">
         <v>7.03987272546481</v>
       </c>
-      <c r="D24">
+      <c r="W24">
         <v>14.135856781628</v>
       </c>
-      <c r="E24">
+      <c r="X24">
+        <v>65.45399999999999</v>
+      </c>
+      <c r="Y24">
+        <v>0.767817564337784</v>
+      </c>
+      <c r="Z24">
+        <v>-3.52163249269094</v>
+      </c>
+      <c r="AA24">
+        <v>-0.681386351585388</v>
+      </c>
+      <c r="AB24">
+        <v>62378410</v>
+      </c>
+      <c r="AD24">
+        <v>-0.185125753283501</v>
+      </c>
+      <c r="AE24">
+        <v>0.0407747849822044</v>
+      </c>
+      <c r="AF24">
         <v>26.0054597822428</v>
       </c>
-      <c r="F24">
+      <c r="AG24">
+        <v>60553113006.2543</v>
+      </c>
+      <c r="AH24">
+        <v>4.91388463271698</v>
+      </c>
+      <c r="AI24">
+        <v>64.7830021330108</v>
+      </c>
+      <c r="AJ24">
         <v>33.268</v>
       </c>
+      <c r="AK24">
+        <v>68.33499999999999</v>
+      </c>
+      <c r="AL24">
+        <v>0.723274409770966</v>
+      </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:38">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
-      <c r="B25">
+      <c r="C25">
+        <v>4.28913865509752</v>
+      </c>
+      <c r="E25">
+        <v>-0.284670442342758</v>
+      </c>
+      <c r="F25">
+        <v>-1.10571242965382</v>
+      </c>
+      <c r="H25">
+        <v>90.54849256431319</v>
+      </c>
+      <c r="I25">
+        <v>32.7545268675424</v>
+      </c>
+      <c r="J25">
+        <v>44.1469911838428</v>
+      </c>
+      <c r="K25">
+        <v>165786604626.3</v>
+      </c>
+      <c r="L25">
         <v>0.698485193724835</v>
       </c>
-      <c r="C25">
+      <c r="M25">
+        <v>15194.1991759502</v>
+      </c>
+      <c r="N25">
+        <v>6022.54254192335</v>
+      </c>
+      <c r="O25">
+        <v>-0.630050659169925</v>
+      </c>
+      <c r="Q25">
+        <v>-0.256946682929993</v>
+      </c>
+      <c r="R25">
+        <v>19.3495643944684</v>
+      </c>
+      <c r="U25">
+        <v>32.4255686814627</v>
+      </c>
+      <c r="V25">
         <v>6.07524384579656</v>
       </c>
-      <c r="F25">
+      <c r="X25">
+        <v>66.139</v>
+      </c>
+      <c r="Y25">
+        <v>0.733136724666569</v>
+      </c>
+      <c r="AA25">
+        <v>-0.665642023086548</v>
+      </c>
+      <c r="AB25">
+        <v>63212384</v>
+      </c>
+      <c r="AD25">
+        <v>-0.223697945475578</v>
+      </c>
+      <c r="AE25">
+        <v>0.08623508363962171</v>
+      </c>
+      <c r="AG25">
+        <v>62491675820.3129</v>
+      </c>
+      <c r="AH25">
+        <v>5.33074985880917</v>
+      </c>
+      <c r="AI25">
+        <v>65.1800955490051</v>
+      </c>
+      <c r="AJ25">
         <v>32.098</v>
       </c>
+      <c r="AK25">
+        <v>68.819</v>
+      </c>
+      <c r="AL25">
+        <v>0.744892179965973</v>
+      </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:38">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
-      <c r="B26">
+      <c r="C26">
+        <v>5.75899180309254</v>
+      </c>
+      <c r="F26">
+        <v>-0.6442198995437181</v>
+      </c>
+      <c r="I26">
+        <v>31.8498451859901</v>
+      </c>
+      <c r="L26">
         <v>0.579853692303914</v>
       </c>
-      <c r="C26">
+      <c r="M26">
+        <v>15457.4891449518</v>
+      </c>
+      <c r="N26">
+        <v>6253.37158194543</v>
+      </c>
+      <c r="O26">
+        <v>-0.669086828300507</v>
+      </c>
+      <c r="R26">
+        <v>19.2310040997797</v>
+      </c>
+      <c r="U26">
+        <v>29.8527528715858</v>
+      </c>
+      <c r="V26">
         <v>4.36115246518963</v>
       </c>
-      <c r="F26">
+      <c r="AB26">
+        <v>64007187</v>
+      </c>
+      <c r="AG26">
+        <v>65434957159.2265</v>
+      </c>
+      <c r="AH26">
+        <v>5.67102712164407</v>
+      </c>
+      <c r="AI26">
+        <v>61.7025980575759</v>
+      </c>
+      <c r="AJ26">
         <v>33.168</v>
+      </c>
+      <c r="AK26">
+        <v>69.298</v>
       </c>
     </row>
   </sheetData>

--- a/ZAF_WB_timeseries.xlsx
+++ b/ZAF_WB_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Control of Corruption</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t>Foreign direct investment, net outflows (BoP, current US$)</t>
+  </si>
+  <si>
+    <t>GDP (current US$)</t>
   </si>
   <si>
     <t>GDP growth (annual %)</t>
@@ -446,12 +449,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y36"/>
+  <dimension ref="A1:Z36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:26">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -525,8 +528,11 @@
       <c r="Y1" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:25">
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26">
       <c r="A2" s="1">
         <v>1990</v>
       </c>
@@ -546,46 +552,49 @@
         <v>27974221.2609344</v>
       </c>
       <c r="J2">
+        <v>126048140141.869</v>
+      </c>
+      <c r="K2">
         <v>-0.317760426540374</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>3093.48920352334</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>17.5888534221331</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>25.4039070668789</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>23.3568517786016</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>16.6732591904381</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>14.3209918914915</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>14.2572632137986</v>
       </c>
-      <c r="S2">
+      <c r="T2">
         <v>-3.15245287878649</v>
       </c>
-      <c r="U2">
+      <c r="V2">
         <v>21.1874515142874</v>
       </c>
-      <c r="V2">
+      <c r="W2">
         <v>2582983157.87227</v>
       </c>
-      <c r="W2">
+      <c r="X2">
         <v>1.19465480077854</v>
       </c>
-      <c r="X2">
+      <c r="Y2">
         <v>38.2118009241798</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:26">
       <c r="A3" s="1">
         <v>1991</v>
       </c>
@@ -605,49 +614,52 @@
         <v>206437797.580551</v>
       </c>
       <c r="J3">
+        <v>135203698237.977</v>
+      </c>
+      <c r="K3">
         <v>-1.0182449675445</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>3243.23616023953</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>17.66995232228</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>24.9351797289334</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>22.6576311137301</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>15.5407939143944</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>15.3347785733672</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>15.4877380683832</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>-3.20833556543633</v>
       </c>
-      <c r="U3">
+      <c r="V3">
         <v>20.9961429260192</v>
       </c>
-      <c r="V3">
+      <c r="W3">
         <v>3186551430.11629</v>
       </c>
-      <c r="W3">
+      <c r="X3">
         <v>1.52429876674072</v>
       </c>
-      <c r="X3">
+      <c r="Y3">
         <v>34.8816092569776</v>
       </c>
-      <c r="Y3">
+      <c r="Z3">
         <v>23.002</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:26">
       <c r="A4" s="1">
         <v>1992</v>
       </c>
@@ -667,49 +679,52 @@
         <v>1939027488.34504</v>
       </c>
       <c r="J4">
+        <v>146956150986.636</v>
+      </c>
+      <c r="K4">
         <v>-2.13703284500521</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>3462.39400202835</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>17.9005585499176</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>27.9224853920467</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>20.9120993698717</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>15.3662068949062</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>13.874703748615</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>15.1193293969871</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>-7.77388868608349</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>18.8799893109627</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <v>3207728532.39078</v>
       </c>
-      <c r="W4">
+      <c r="X4">
         <v>1.45376401915937</v>
       </c>
-      <c r="X4">
+      <c r="Y4">
         <v>34.3213534993474</v>
       </c>
-      <c r="Y4">
+      <c r="Z4">
         <v>23.262</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:26">
       <c r="A5" s="1">
         <v>1993</v>
       </c>
@@ -729,52 +744,55 @@
         <v>291914248.53766</v>
       </c>
       <c r="J5">
+        <v>147194747565.75</v>
+      </c>
+      <c r="K5">
         <v>1.23355793864741</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>3399.64009566241</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>59.3</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>18.1205609764085</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>29.153558307063</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>21.6283156898605</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>15.7837577150899</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>9.717427298030261</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>15.5654759782353</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>-8.078679346315999</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>19.8688359609019</v>
       </c>
-      <c r="V5">
+      <c r="W5">
         <v>2879214919.10976</v>
       </c>
-      <c r="W5">
+      <c r="X5">
         <v>1.30157267285546</v>
       </c>
-      <c r="X5">
+      <c r="Y5">
         <v>35.6981243460429</v>
       </c>
-      <c r="Y5">
+      <c r="Z5">
         <v>23.179</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:26">
       <c r="A6" s="1">
         <v>1994</v>
       </c>
@@ -800,49 +818,52 @@
         <v>1260506545.07751</v>
       </c>
       <c r="J6">
+        <v>153512712381.836</v>
+      </c>
+      <c r="K6">
         <v>3.20000000297172</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>3488.59711541763</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>18.1888688750082</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>25.8102919971572</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>21.3189452868409</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>17.5652713615169</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>8.938563723593999</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <v>16.7773118203142</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <v>-4.84119550439251</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>19.6043743222704</v>
       </c>
-      <c r="V6">
+      <c r="W6">
         <v>3294868535.33399</v>
       </c>
-      <c r="W6">
+      <c r="X6">
         <v>1.30339237556196</v>
       </c>
-      <c r="X6">
+      <c r="Y6">
         <v>37.1146091666279</v>
       </c>
-      <c r="Y6">
+      <c r="Z6">
         <v>22.942</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:26">
       <c r="A7" s="1">
         <v>1995</v>
       </c>
@@ -868,49 +889,52 @@
         <v>2493914011.35083</v>
       </c>
       <c r="J7">
+        <v>171735933897.331</v>
+      </c>
+      <c r="K7">
         <v>3.10000000054411</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>3855.6340871567</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>16.5269303515062</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>26.0917937855667</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>22.0235699547948</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>19.4401731715272</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>8.680424213926329</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <v>18.25123364877</v>
       </c>
-      <c r="S7">
+      <c r="T7">
         <v>-4.80429605618098</v>
       </c>
-      <c r="U7">
+      <c r="V7">
         <v>20.2955260214681</v>
       </c>
-      <c r="V7">
+      <c r="W7">
         <v>4463556727.10403</v>
       </c>
-      <c r="W7">
+      <c r="X7">
         <v>1.43270061747907</v>
       </c>
-      <c r="X7">
+      <c r="Y7">
         <v>39.4780337793026</v>
       </c>
-      <c r="Y7">
+      <c r="Z7">
         <v>22.647</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:26">
       <c r="A8" s="1">
         <v>1996</v>
       </c>
@@ -939,52 +963,55 @@
         <v>1047974476.01688</v>
       </c>
       <c r="J8">
+        <v>163234925380.563</v>
+      </c>
+      <c r="K8">
         <v>4.29999999726792</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>3617.55336002932</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>17.4247248982139</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>27.0184443878932</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>22.9647545373647</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>20.4245085135556</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>7.35411972085331</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>17.5870770739888</v>
       </c>
-      <c r="S8">
+      <c r="T8">
         <v>-4.66611162805924</v>
       </c>
-      <c r="T8">
+      <c r="U8">
         <v>-0.379187554121017</v>
       </c>
-      <c r="U8">
+      <c r="V8">
         <v>20.9846364817904</v>
       </c>
-      <c r="V8">
+      <c r="W8">
         <v>2341014432.71495</v>
       </c>
-      <c r="W8">
+      <c r="X8">
         <v>0.749182306824821</v>
       </c>
-      <c r="X8">
+      <c r="Y8">
         <v>42.199251732528</v>
       </c>
-      <c r="Y8">
+      <c r="Z8">
         <v>22.48</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:26">
       <c r="A9" s="1">
         <v>1997</v>
       </c>
@@ -1010,49 +1037,52 @@
         <v>2323603598.20082</v>
       </c>
       <c r="J9">
+        <v>168978057327.73</v>
+      </c>
+      <c r="K9">
         <v>2.60000000146347</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>3700.23554789867</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>17.4918768157123</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>25.8104575987438</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>23.054873900491</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>20.6407425739789</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>8.59777611252273</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>19.4221375447389</v>
       </c>
-      <c r="S9">
+      <c r="T9">
         <v>-3.3619580064389</v>
       </c>
-      <c r="U9">
+      <c r="V9">
         <v>21.2498395625278</v>
       </c>
-      <c r="V9">
+      <c r="W9">
         <v>5957312964.3435</v>
       </c>
-      <c r="W9">
+      <c r="X9">
         <v>1.81151705227386</v>
       </c>
-      <c r="X9">
+      <c r="Y9">
         <v>42.3013344291831</v>
       </c>
-      <c r="Y9">
+      <c r="Z9">
         <v>22.518</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:26">
       <c r="A10" s="1">
         <v>1998</v>
       </c>
@@ -1081,52 +1111,55 @@
         <v>1634005239.21987</v>
       </c>
       <c r="J10">
+        <v>152982984557.233</v>
+      </c>
+      <c r="K10">
         <v>0.50000000034143</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>3309.60933087472</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>17.1000261817972</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>25.6771109721042</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>23.5980988040593</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>21.5164735193548</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <v>6.88054521037351</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <v>19.7476605947967</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>-2.64728818513197</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <v>-0.546053230762482</v>
       </c>
-      <c r="U10">
+      <c r="V10">
         <v>21.9639431431796</v>
       </c>
-      <c r="V10">
+      <c r="W10">
         <v>5508053230.71678</v>
       </c>
-      <c r="W10">
+      <c r="X10">
         <v>1.76142933259018</v>
       </c>
-      <c r="X10">
+      <c r="Y10">
         <v>44.0357453368965</v>
       </c>
-      <c r="Y10">
+      <c r="Z10">
         <v>22.673</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:26">
       <c r="A11" s="1">
         <v>1999</v>
       </c>
@@ -1152,49 +1185,52 @@
         <v>1584183080.40416</v>
       </c>
       <c r="J11">
+        <v>151516957078.536</v>
+      </c>
+      <c r="K11">
         <v>2.39999999746338</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>3242.36830483958</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>16.8105311881129</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>25.3033512796678</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>24.085492728306</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>19.9890800426071</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>5.18148905111698</v>
       </c>
-      <c r="R11">
+      <c r="S11">
         <v>18.9121238163913</v>
       </c>
-      <c r="S11">
+      <c r="T11">
         <v>-1.59283272266752</v>
       </c>
-      <c r="U11">
+      <c r="V11">
         <v>21.7599312426722</v>
       </c>
-      <c r="V11">
+      <c r="W11">
         <v>7496680479.60889</v>
       </c>
-      <c r="W11">
+      <c r="X11">
         <v>2.54961732709242</v>
       </c>
-      <c r="X11">
+      <c r="Y11">
         <v>42.2582960172673</v>
       </c>
-      <c r="Y11">
+      <c r="Z11">
         <v>22.791</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:26">
       <c r="A12" s="1">
         <v>2000</v>
       </c>
@@ -1223,55 +1259,58 @@
         <v>277178617.396324</v>
       </c>
       <c r="J12">
+        <v>151752757215.309</v>
+      </c>
+      <c r="K12">
         <v>4.20000000067826</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>3217.84693448467</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>57.8</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>16.5672154108403</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>24.4358091522258</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>23.0698153754344</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>21.8164184247158</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>5.33895913599827</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>18.1060049086277</v>
       </c>
-      <c r="S12">
+      <c r="T12">
         <v>-1.71684047324677</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <v>-0.227864950895309</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <v>20.9760632464162</v>
       </c>
-      <c r="V12">
+      <c r="W12">
         <v>7702061131.77162</v>
       </c>
-      <c r="W12">
+      <c r="X12">
         <v>2.38388518393691</v>
       </c>
-      <c r="X12">
+      <c r="Y12">
         <v>46.2207217354077</v>
       </c>
-      <c r="Y12">
+      <c r="Z12">
         <v>22.714</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:26">
       <c r="A13" s="1">
         <v>2001</v>
       </c>
@@ -1294,49 +1333,52 @@
         <v>-3514732729.23594</v>
       </c>
       <c r="J13">
+        <v>135429905922.526</v>
+      </c>
+      <c r="K13">
         <v>2.70000000019104</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>2847.15191945908</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>16.6218512164789</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>24.3412920517984</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>24.0019951706408</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>22.8142845512603</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>5.70189483049609</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <v>16.8016772079421</v>
       </c>
-      <c r="S13">
+      <c r="T13">
         <v>-0.8019276640098471</v>
       </c>
-      <c r="U13">
+      <c r="V13">
         <v>21.7005914264295</v>
       </c>
-      <c r="V13">
+      <c r="W13">
         <v>7626856919.15025</v>
       </c>
-      <c r="W13">
+      <c r="X13">
         <v>2.45317346788814</v>
       </c>
-      <c r="X13">
+      <c r="Y13">
         <v>49.170945185829</v>
       </c>
-      <c r="Y13">
+      <c r="Z13">
         <v>22.605</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:26">
       <c r="A14" s="1">
         <v>2002</v>
       </c>
@@ -1362,52 +1404,55 @@
         <v>-402262421.186722</v>
       </c>
       <c r="J14">
+        <v>129087556612.449</v>
+      </c>
+      <c r="K14">
         <v>3.70037440406668</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>2688.23676032806</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>16.7803880295906</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>23.6803783151852</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>22.7016759682254</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>25.0343344117566</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>9.494713780995999</v>
       </c>
-      <c r="R14">
+      <c r="S14">
         <v>14.5583370058408</v>
       </c>
-      <c r="S14">
+      <c r="T14">
         <v>-1.39209881025107</v>
       </c>
-      <c r="T14">
+      <c r="U14">
         <v>-0.254789859056473</v>
       </c>
-      <c r="U14">
+      <c r="V14">
         <v>20.8248927712355</v>
       </c>
-      <c r="V14">
+      <c r="W14">
         <v>7816784858.41019</v>
       </c>
-      <c r="W14">
+      <c r="X14">
         <v>2.50168882524225</v>
       </c>
-      <c r="X14">
+      <c r="Y14">
         <v>53.4655016294369</v>
       </c>
-      <c r="Y14">
+      <c r="Z14">
         <v>22.547</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:26">
       <c r="A15" s="1">
         <v>2003</v>
       </c>
@@ -1433,52 +1478,55 @@
         <v>552543632.214808</v>
       </c>
       <c r="J15">
+        <v>197018965308.697</v>
+      </c>
+      <c r="K15">
         <v>2.94907546754213</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>4062.21755993786</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>16.8663209712168</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>24.7704671599849</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>22.7024907610567</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>21.8085892075755</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>5.679424140688</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <v>12.5691941140716</v>
       </c>
-      <c r="S15">
+      <c r="T15">
         <v>-2.26456368589691</v>
       </c>
-      <c r="T15">
+      <c r="U15">
         <v>-0.312842577695847</v>
       </c>
-      <c r="U15">
+      <c r="V15">
         <v>20.4927670870354</v>
       </c>
-      <c r="V15">
+      <c r="W15">
         <v>8154089032.58033</v>
       </c>
-      <c r="W15">
+      <c r="X15">
         <v>1.92764823872227</v>
       </c>
-      <c r="X15">
+      <c r="Y15">
         <v>45.723862568979</v>
       </c>
-      <c r="Y15">
+      <c r="Z15">
         <v>22.629</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:26">
       <c r="A16" s="1">
         <v>2004</v>
       </c>
@@ -1504,52 +1552,55 @@
         <v>1305424326.22046</v>
       </c>
       <c r="J16">
+        <v>255806908594.573</v>
+      </c>
+      <c r="K16">
         <v>4.55455990721774</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>5221.46333731721</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>17.0044389815087</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>25.6020497773113</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>24.0807788202014</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>22.8860564383387</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>-0.692039437857689</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <v>11.5613262515453</v>
       </c>
-      <c r="S16">
+      <c r="T16">
         <v>-1.68236664045094</v>
       </c>
-      <c r="T16">
+      <c r="U16">
         <v>-0.131729558110237</v>
       </c>
-      <c r="U16">
+      <c r="V16">
         <v>21.6985960707513</v>
       </c>
-      <c r="V16">
+      <c r="W16">
         <v>14886243628.1943</v>
       </c>
-      <c r="W16">
+      <c r="X16">
         <v>2.68935775221081</v>
       </c>
-      <c r="X16">
+      <c r="Y16">
         <v>45.6435752240041</v>
       </c>
-      <c r="Y16">
+      <c r="Z16">
         <v>22.538</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:26">
       <c r="A17" s="1">
         <v>2005</v>
       </c>
@@ -1575,55 +1626,58 @@
         <v>909414375.58636</v>
       </c>
       <c r="J17">
+        <v>288867217196.534</v>
+      </c>
+      <c r="K17">
         <v>5.27705197295467</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>5836.87663325127</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>64.8</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>16.1488985315911</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>25.6017227017192</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>25.7301385005501</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>23.8280169054893</v>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <v>2.06285308223427</v>
       </c>
-      <c r="R17">
+      <c r="S17">
         <v>10.8593590528679</v>
       </c>
-      <c r="S17">
+      <c r="T17">
         <v>-0.161839834643574</v>
       </c>
-      <c r="T17">
+      <c r="U17">
         <v>-0.162092119455338</v>
       </c>
-      <c r="U17">
+      <c r="V17">
         <v>22.9721111805983</v>
       </c>
-      <c r="V17">
+      <c r="W17">
         <v>20624460695.2026</v>
       </c>
-      <c r="W17">
+      <c r="X17">
         <v>3.16114379578521</v>
       </c>
-      <c r="X17">
+      <c r="Y17">
         <v>47.4277813970329</v>
       </c>
-      <c r="Y17">
+      <c r="Z17">
         <v>22.461</v>
       </c>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:26">
       <c r="A18" s="1">
         <v>2006</v>
       </c>
@@ -1649,52 +1703,55 @@
         <v>5928796515.33873</v>
       </c>
       <c r="J18">
+        <v>303858675363.643</v>
+      </c>
+      <c r="K18">
         <v>5.60380645895889</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>6077.38293388876</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>15.8607403931821</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>25.8417852811827</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>26.9292690601181</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>27.6698913924026</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <v>3.24390765419229</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <v>9.850315674256519</v>
       </c>
-      <c r="S18">
+      <c r="T18">
         <v>0.781786917588248</v>
       </c>
-      <c r="T18">
+      <c r="U18">
         <v>0.0470300763845444</v>
       </c>
-      <c r="U18">
+      <c r="V18">
         <v>24.3780853808343</v>
       </c>
-      <c r="V18">
+      <c r="W18">
         <v>25593361431.1639</v>
       </c>
-      <c r="W18">
+      <c r="X18">
         <v>3.23727857447778</v>
       </c>
-      <c r="X18">
+      <c r="Y18">
         <v>53.7681412741145</v>
       </c>
-      <c r="Y18">
+      <c r="Z18">
         <v>22.324</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:26">
       <c r="A19" s="1">
         <v>2007</v>
       </c>
@@ -1720,52 +1777,55 @@
         <v>2982112484.38287</v>
       </c>
       <c r="J19">
+        <v>333077117253.684</v>
+      </c>
+      <c r="K19">
         <v>5.36047405394162</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>6591.85535960564</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>15.8864978575358</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>26.0805418540207</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>27.2583059687972</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>29.166174743045</v>
       </c>
-      <c r="Q19">
+      <c r="R19">
         <v>6.17781214809388</v>
       </c>
-      <c r="R19">
+      <c r="S19">
         <v>8.673096750264291</v>
       </c>
-      <c r="S19">
+      <c r="T19">
         <v>0.924679916294093</v>
       </c>
-      <c r="T19">
+      <c r="U19">
         <v>0.215346544981003</v>
       </c>
-      <c r="U19">
+      <c r="V19">
         <v>24.8072372824336</v>
       </c>
-      <c r="V19">
+      <c r="W19">
         <v>32919403650.564</v>
       </c>
-      <c r="W19">
+      <c r="X19">
         <v>3.46397510382695</v>
       </c>
-      <c r="X19">
+      <c r="Y19">
         <v>57.125139137747</v>
       </c>
-      <c r="Y19">
+      <c r="Z19">
         <v>22.287</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:26">
       <c r="A20" s="1">
         <v>2008</v>
       </c>
@@ -1791,55 +1851,58 @@
         <v>-2119582844.48363</v>
       </c>
       <c r="J20">
+        <v>316131258616.309</v>
+      </c>
+      <c r="K20">
         <v>3.1910438863288</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>6184.75474328399</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>63</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>17.0724538163321</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>27.1771183464084</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>26.8712941110509</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>33.7198501285556</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>9.909984560054671</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <v>7.6976073804606</v>
       </c>
-      <c r="S20">
+      <c r="T20">
         <v>-0.5890955128302749</v>
       </c>
-      <c r="T20">
+      <c r="U20">
         <v>0.049528993666172</v>
       </c>
-      <c r="U20">
+      <c r="V20">
         <v>24.322809870073</v>
       </c>
-      <c r="V20">
+      <c r="W20">
         <v>34070371606.9593</v>
       </c>
-      <c r="W20">
+      <c r="X20">
         <v>3.3280835307273</v>
       </c>
-      <c r="X20">
+      <c r="Y20">
         <v>65.9745237996233</v>
       </c>
-      <c r="Y20">
+      <c r="Z20">
         <v>22.407</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
+    <row r="21" spans="1:26">
       <c r="A21" s="1">
         <v>2009</v>
       </c>
@@ -1865,52 +1928,55 @@
         <v>1311299639.40389</v>
       </c>
       <c r="J21">
+        <v>329754060647.129</v>
+      </c>
+      <c r="K21">
         <v>-1.53808913525583</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>6374.70560042992</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>17.7936331368919</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>29.1019033706759</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>24.9965390873939</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>24.6047888395564</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>7.23809523809527</v>
       </c>
-      <c r="R21">
+      <c r="S21">
         <v>7.31227235926203</v>
       </c>
-      <c r="S21">
+      <c r="T21">
         <v>-4.46450848490938</v>
       </c>
-      <c r="T21">
+      <c r="U21">
         <v>-0.114492610096931</v>
       </c>
-      <c r="U21">
+      <c r="V21">
         <v>21.8948743006162</v>
       </c>
-      <c r="V21">
+      <c r="W21">
         <v>39602644576.4755</v>
       </c>
-      <c r="W21">
+      <c r="X21">
         <v>5.12662348081341</v>
       </c>
-      <c r="X21">
+      <c r="Y21">
         <v>49.5875353278801</v>
       </c>
-      <c r="Y21">
+      <c r="Z21">
         <v>23.523</v>
       </c>
     </row>
-    <row r="22" spans="1:25">
+    <row r="22" spans="1:26">
       <c r="A22" s="1">
         <v>2010</v>
       </c>
@@ -1936,55 +2002,58 @@
         <v>-161293236.931745</v>
       </c>
       <c r="J22">
+        <v>417363822801.713</v>
+      </c>
+      <c r="K22">
         <v>3.03973288127956</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>7973.47195771517</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>63.4</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>17.996063602882</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>29.5775128260769</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>25.5192267165858</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>24.6226695358778</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>4.06749555950264</v>
       </c>
-      <c r="R22">
+      <c r="S22">
         <v>7.68019097019604</v>
       </c>
-      <c r="S22">
+      <c r="T22">
         <v>-4.44267265987095</v>
       </c>
-      <c r="T22">
+      <c r="U22">
         <v>-0.0294270031154156</v>
       </c>
-      <c r="U22">
+      <c r="V22">
         <v>22.5206038776132</v>
       </c>
-      <c r="V22">
+      <c r="W22">
         <v>43819545749.0238</v>
       </c>
-      <c r="W22">
+      <c r="X22">
         <v>4.54059848802417</v>
       </c>
-      <c r="X22">
+      <c r="Y22">
         <v>50.4060871625999</v>
       </c>
-      <c r="Y22">
+      <c r="Z22">
         <v>24.683</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:26">
       <c r="A23" s="1">
         <v>2011</v>
       </c>
@@ -2010,52 +2079,55 @@
         <v>-153398301.646755</v>
       </c>
       <c r="J23">
+        <v>458199494830.834</v>
+      </c>
+      <c r="K23">
         <v>3.16855627858818</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>8646.055710716349</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>18.1951431854763</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>31.0619734464171</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>25.9740547550987</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>26.9382019655219</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>5.00085338795019</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <v>7.90376276286169</v>
       </c>
-      <c r="S23">
+      <c r="T23">
         <v>-5.46206329752573</v>
       </c>
-      <c r="T23">
+      <c r="U23">
         <v>0.0240315701812506</v>
       </c>
-      <c r="U23">
+      <c r="V23">
         <v>22.8746700116825</v>
       </c>
-      <c r="V23">
+      <c r="W23">
         <v>48748260246.0381</v>
       </c>
-      <c r="W23">
+      <c r="X23">
         <v>4.19180307031225</v>
       </c>
-      <c r="X23">
+      <c r="Y23">
         <v>54.6363504358971</v>
       </c>
-      <c r="Y23">
+      <c r="Z23">
         <v>24.639</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
+    <row r="24" spans="1:26">
       <c r="A24" s="1">
         <v>2012</v>
       </c>
@@ -2081,52 +2153,55 @@
         <v>2898869629.96875</v>
       </c>
       <c r="J24">
+        <v>434400545085.811</v>
+      </c>
+      <c r="K24">
         <v>2.39623238465745</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>8076.97678479741</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>18.8205452606488</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>30.3651797341743</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>26.5227856834625</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>28.4434679995666</v>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <v>5.73797139141737</v>
       </c>
-      <c r="R24">
+      <c r="S24">
         <v>8.7038710886434</v>
       </c>
-      <c r="S24">
+      <c r="T24">
         <v>-4.23209308673638</v>
       </c>
-      <c r="T24">
+      <c r="U24">
         <v>-0.0253867004066706</v>
       </c>
-      <c r="U24">
+      <c r="V24">
         <v>23.3457659894736</v>
       </c>
-      <c r="V24">
+      <c r="W24">
         <v>50688078405.0297</v>
       </c>
-      <c r="W24">
+      <c r="X24">
         <v>4.33171873217314</v>
       </c>
-      <c r="X24">
+      <c r="Y24">
         <v>55.5826171933345</v>
       </c>
-      <c r="Y24">
+      <c r="Z24">
         <v>24.727</v>
       </c>
     </row>
-    <row r="25" spans="1:25">
+    <row r="25" spans="1:26">
       <c r="A25" s="1">
         <v>2013</v>
       </c>
@@ -2152,52 +2227,55 @@
         <v>6519873357.51593</v>
       </c>
       <c r="J25">
+        <v>400886013595.573</v>
+      </c>
+      <c r="K25">
         <v>2.48546800826588</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>7331.65467384919</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>19.0813745546722</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>31.259190573785</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>27.4101862231804</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>30.4957473096901</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <v>5.78016910069177</v>
       </c>
-      <c r="R25">
+      <c r="S25">
         <v>8.737755337317539</v>
       </c>
-      <c r="S25">
+      <c r="T25">
         <v>-4.18299310803963</v>
       </c>
-      <c r="T25">
+      <c r="U25">
         <v>-0.0462945364415646</v>
       </c>
-      <c r="U25">
+      <c r="V25">
         <v>23.831391363238</v>
       </c>
-      <c r="V25">
+      <c r="W25">
         <v>49708174893.5691</v>
       </c>
-      <c r="W25">
+      <c r="X25">
         <v>4.30463726127469</v>
       </c>
-      <c r="X25">
+      <c r="Y25">
         <v>58.875027630051</v>
       </c>
-      <c r="Y25">
+      <c r="Z25">
         <v>24.561</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:26">
       <c r="A26" s="1">
         <v>2014</v>
       </c>
@@ -2223,55 +2301,58 @@
         <v>7692076889.07783</v>
       </c>
       <c r="J26">
+        <v>381198869776.106</v>
+      </c>
+      <c r="K26">
         <v>1.41382645223793</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>6856.73137092522</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>63</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>19.3140625940978</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>31.9053501556958</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>28.8726130567165</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>30.4989547517121</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <v>6.13282953059149</v>
       </c>
-      <c r="R26">
+      <c r="S26">
         <v>9.179413341109409</v>
       </c>
-      <c r="S26">
+      <c r="T26">
         <v>-3.43956150956061</v>
       </c>
-      <c r="T26">
+      <c r="U26">
         <v>-0.146388962864876</v>
       </c>
-      <c r="U26">
+      <c r="V26">
         <v>24.4319342176034</v>
       </c>
-      <c r="V26">
+      <c r="W26">
         <v>49121568380.4854</v>
       </c>
-      <c r="W26">
+      <c r="X26">
         <v>4.42516066122754</v>
       </c>
-      <c r="X26">
+      <c r="Y26">
         <v>59.4995740550593</v>
       </c>
-      <c r="Y26">
+      <c r="Z26">
         <v>24.89</v>
       </c>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:26">
       <c r="A27" s="1">
         <v>2015</v>
       </c>
@@ -2300,52 +2381,55 @@
         <v>5514928846.02681</v>
       </c>
       <c r="J27">
+        <v>346709790458.563</v>
+      </c>
+      <c r="K27">
         <v>1.32186223678229</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>6112.27382485974</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>18.9850713286308</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>33.6797787454907</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>29.6472581887112</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>29.0130377322327</v>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <v>4.5186909489251</v>
       </c>
-      <c r="R27">
+      <c r="S27">
         <v>9.098965099900539</v>
       </c>
-      <c r="S27">
+      <c r="T27">
         <v>-4.56437663555894</v>
       </c>
-      <c r="T27">
+      <c r="U27">
         <v>-0.220544874668121</v>
       </c>
-      <c r="U27">
+      <c r="V27">
         <v>25.0486927031144</v>
       </c>
-      <c r="V27">
+      <c r="W27">
         <v>45887065756.7249</v>
       </c>
-      <c r="W27">
+      <c r="X27">
         <v>4.724214132513</v>
       </c>
-      <c r="X27">
+      <c r="Y27">
         <v>56.7266761447156</v>
       </c>
-      <c r="Y27">
+      <c r="Z27">
         <v>25.149</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:26">
       <c r="A28" s="1">
         <v>2016</v>
       </c>
@@ -2374,52 +2458,55 @@
         <v>4490478135.44758</v>
       </c>
       <c r="J28">
+        <v>323585509674.481</v>
+      </c>
+      <c r="K28">
         <v>0.664552307858116</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>5651.20585165749</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>19.3075616545523</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>32.1896608002111</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>29.0406590015195</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>27.7051693349827</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <v>6.60290842394869</v>
       </c>
-      <c r="R28">
+      <c r="S28">
         <v>10.2150196800716</v>
       </c>
-      <c r="S28">
+      <c r="T28">
         <v>-3.46049874466043</v>
       </c>
-      <c r="T28">
+      <c r="U28">
         <v>-0.149085000157356</v>
       </c>
-      <c r="U28">
+      <c r="V28">
         <v>24.8283559884696</v>
       </c>
-      <c r="V28">
+      <c r="W28">
         <v>47180127300.8565</v>
       </c>
-      <c r="W28">
+      <c r="X28">
         <v>5.43700662124582</v>
       </c>
-      <c r="X28">
+      <c r="Y28">
         <v>55.8612575048782</v>
       </c>
-      <c r="Y28">
+      <c r="Z28">
         <v>26.536</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:26">
       <c r="A29" s="1">
         <v>2017</v>
       </c>
@@ -2448,52 +2535,55 @@
         <v>7449223483.92817</v>
       </c>
       <c r="J29">
+        <v>381448814653.456</v>
+      </c>
+      <c r="K29">
         <v>1.15794695181735</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>6618.33508255701</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>19.2360771279531</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>33.2518124768773</v>
       </c>
-      <c r="O29">
+      <c r="P29">
         <v>28.9131558196206</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>26.1958560481525</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <v>5.18618655524146</v>
       </c>
-      <c r="R29">
+      <c r="S29">
         <v>10.5634519284442</v>
       </c>
-      <c r="S29">
+      <c r="T29">
         <v>-4.65754447743392</v>
       </c>
-      <c r="T29">
+      <c r="U29">
         <v>-0.284803628921509</v>
       </c>
-      <c r="U29">
+      <c r="V29">
         <v>24.76928728931</v>
       </c>
-      <c r="V29">
+      <c r="W29">
         <v>50722891363.2361</v>
       </c>
-      <c r="W29">
+      <c r="X29">
         <v>5.2254571809234</v>
       </c>
-      <c r="X29">
+      <c r="Y29">
         <v>53.5359318293741</v>
       </c>
-      <c r="Y29">
+      <c r="Z29">
         <v>27.035</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:26">
       <c r="A30" s="1">
         <v>2018</v>
       </c>
@@ -2522,52 +2612,55 @@
         <v>4026961507.92187</v>
       </c>
       <c r="J30">
+        <v>405260723892.517</v>
+      </c>
+      <c r="K30">
         <v>1.55678384721676</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>6914.1780318076</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>19.352226142463</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>33.9954978254972</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>28.3643368318902</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>26.9885079767917</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>4.50987264867393</v>
       </c>
-      <c r="R30">
+      <c r="S30">
         <v>10.5625640407853</v>
       </c>
-      <c r="S30">
+      <c r="T30">
         <v>-5.69551397247214</v>
       </c>
-      <c r="T30">
+      <c r="U30">
         <v>-0.237546816468239</v>
       </c>
-      <c r="U30">
+      <c r="V30">
         <v>24.8948940727422</v>
       </c>
-      <c r="V30">
+      <c r="W30">
         <v>51642041966.6735</v>
       </c>
-      <c r="W30">
+      <c r="X30">
         <v>4.81246249518313</v>
       </c>
-      <c r="X30">
+      <c r="Y30">
         <v>54.4855451276341</v>
       </c>
-      <c r="Y30">
+      <c r="Z30">
         <v>26.906</v>
       </c>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:26">
       <c r="A31" s="1">
         <v>2019</v>
       </c>
@@ -2596,52 +2689,55 @@
         <v>3140937957.42651</v>
       </c>
       <c r="J31">
+        <v>389330032224.269</v>
+      </c>
+      <c r="K31">
         <v>0.25993557687633</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>6533.71121032856</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>19.5800800398681</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>34.6532754617872</v>
       </c>
-      <c r="O31">
+      <c r="P31">
         <v>28.8976157499402</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>26.6958670030255</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <v>4.1028507546115</v>
       </c>
-      <c r="R31">
+      <c r="S31">
         <v>11.041411159621</v>
       </c>
-      <c r="S31">
+      <c r="T31">
         <v>-5.75192703897</v>
       </c>
-      <c r="T31">
+      <c r="U31">
         <v>-0.2832210958004</v>
       </c>
-      <c r="U31">
+      <c r="V31">
         <v>24.8673453267976</v>
       </c>
-      <c r="V31">
+      <c r="W31">
         <v>55055893656.867</v>
       </c>
-      <c r="W31">
+      <c r="X31">
         <v>5.40690081512174</v>
       </c>
-      <c r="X31">
+      <c r="Y31">
         <v>53.8979964081406</v>
       </c>
-      <c r="Y31">
+      <c r="Z31">
         <v>28.468</v>
       </c>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:26">
       <c r="A32" s="1">
         <v>2020</v>
       </c>
@@ -2670,52 +2766,55 @@
         <v>-1935862273.31753</v>
       </c>
       <c r="J32">
+        <v>337974655408.055</v>
+      </c>
+      <c r="K32">
         <v>-6.1689177146757</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>5580.60383075189</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>20.6203398698938</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>37.8354162011745</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>27.8138753889078</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>23.1837449200214</v>
       </c>
-      <c r="Q32">
+      <c r="R32">
         <v>3.23238831615119</v>
       </c>
-      <c r="R32">
+      <c r="S32">
         <v>11.4297572612146</v>
       </c>
-      <c r="S32">
+      <c r="T32">
         <v>-9.92664872393274</v>
       </c>
-      <c r="T32">
+      <c r="U32">
         <v>-0.252867221832275</v>
       </c>
-      <c r="U32">
+      <c r="V32">
         <v>23.2649440409195</v>
       </c>
-      <c r="V32">
+      <c r="W32">
         <v>55008491995.5568</v>
       </c>
-      <c r="W32">
+      <c r="X32">
         <v>7.12354295570033</v>
       </c>
-      <c r="X32">
+      <c r="Y32">
         <v>50.7596590804177</v>
       </c>
-      <c r="Y32">
+      <c r="Z32">
         <v>29.217</v>
       </c>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:26">
       <c r="A33" s="1">
         <v>2021</v>
       </c>
@@ -2744,52 +2843,55 @@
         <v>101577294.28811</v>
       </c>
       <c r="J33">
+        <v>420886877628.703</v>
+      </c>
+      <c r="K33">
         <v>4.95503259440756</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>6843.39941886204</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>19.1782663776178</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>34.53100888431</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>30.0652667080962</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>24.9311150310516</v>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <v>4.61874544887136</v>
       </c>
-      <c r="R33">
+      <c r="S33">
         <v>12.92388692824</v>
       </c>
-      <c r="S33">
+      <c r="T33">
         <v>-4.49568737459651</v>
       </c>
-      <c r="T33">
+      <c r="U33">
         <v>-0.750981450080872</v>
       </c>
-      <c r="U33">
+      <c r="V33">
         <v>25.8946273252854</v>
       </c>
-      <c r="V33">
+      <c r="W33">
         <v>57597149617.2517</v>
       </c>
-      <c r="W33">
+      <c r="X33">
         <v>5.56291275582496</v>
       </c>
-      <c r="X33">
+      <c r="Y33">
         <v>56.0347138372399</v>
       </c>
-      <c r="Y33">
+      <c r="Z33">
         <v>34.007</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:26">
       <c r="A34" s="1">
         <v>2022</v>
       </c>
@@ -2818,52 +2920,55 @@
         <v>2374634495.38148</v>
       </c>
       <c r="J34">
+        <v>406920004594.074</v>
+      </c>
+      <c r="K34">
         <v>1.91147996033504</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>6523.41097815853</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>18.9892702779701</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>33.4798352578178</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>30.273151278645</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>31.4115525789563</v>
       </c>
-      <c r="Q34">
+      <c r="R34">
         <v>7.03987272546481</v>
       </c>
-      <c r="R34">
+      <c r="S34">
         <v>14.135856781628</v>
       </c>
-      <c r="S34">
+      <c r="T34">
         <v>-3.52163249269094</v>
       </c>
-      <c r="T34">
+      <c r="U34">
         <v>-0.681386351585388</v>
       </c>
-      <c r="U34">
+      <c r="V34">
         <v>26.0054597822428</v>
       </c>
-      <c r="V34">
+      <c r="W34">
         <v>60553113006.2543</v>
       </c>
-      <c r="W34">
+      <c r="X34">
         <v>4.91388463271698</v>
       </c>
-      <c r="X34">
+      <c r="Y34">
         <v>64.7830021330108</v>
       </c>
-      <c r="Y34">
+      <c r="Z34">
         <v>33.268</v>
       </c>
     </row>
-    <row r="35" spans="1:25">
+    <row r="35" spans="1:26">
       <c r="A35" s="1">
         <v>2023</v>
       </c>
@@ -2889,37 +2994,40 @@
         <v>-2793247126.44699</v>
       </c>
       <c r="J35">
+        <v>380699271816.395</v>
+      </c>
+      <c r="K35">
         <v>0.698485193724835</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>6022.54254192335</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>19.3495643944684</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
         <v>32.4255686814627</v>
       </c>
-      <c r="Q35">
+      <c r="R35">
         <v>6.07524384579656</v>
       </c>
-      <c r="T35">
+      <c r="U35">
         <v>-0.665642023086548</v>
       </c>
-      <c r="V35">
+      <c r="W35">
         <v>62491675820.3129</v>
       </c>
-      <c r="W35">
+      <c r="X35">
         <v>5.33074985880917</v>
       </c>
-      <c r="X35">
+      <c r="Y35">
         <v>65.1800955490051</v>
       </c>
-      <c r="Y35">
+      <c r="Z35">
         <v>32.098</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:26">
       <c r="A36" s="1">
         <v>2024</v>
       </c>
@@ -2936,30 +3044,33 @@
         <v>-1263888360.92627</v>
       </c>
       <c r="J36">
+        <v>400260724226.067</v>
+      </c>
+      <c r="K36">
         <v>0.579853692303914</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>6253.37158194543</v>
       </c>
-      <c r="M36">
+      <c r="N36">
         <v>19.2310040997797</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
         <v>29.8527528715858</v>
       </c>
-      <c r="Q36">
+      <c r="R36">
         <v>4.36115246518963</v>
       </c>
-      <c r="V36">
+      <c r="W36">
         <v>65434957159.2265</v>
       </c>
-      <c r="W36">
+      <c r="X36">
         <v>5.67102712164407</v>
       </c>
-      <c r="X36">
+      <c r="Y36">
         <v>61.7025980575759</v>
       </c>
-      <c r="Y36">
+      <c r="Z36">
         <v>33.168</v>
       </c>
     </row>

--- a/ZAF_WB_timeseries.xlsx
+++ b/ZAF_WB_timeseries.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beldjenna/Desktop/Rating Algo/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C575944-FF8F-8C4C-A521-C81CE848677B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -73,8 +67,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,18 +85,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -132,33 +120,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -196,7 +175,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -230,7 +209,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -265,10 +243,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -441,11 +418,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -495,61 +472,60 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
       <c r="B2">
-        <v>0.55026972293853804</v>
+        <v>0.550269722938538</v>
       </c>
       <c r="C2">
-        <v>-0.12557045965334701</v>
+        <v>-0.125570459653347</v>
       </c>
       <c r="D2">
         <v>37.9</v>
       </c>
       <c r="E2">
-        <v>24.404303310691901</v>
+        <v>24.4043033106919</v>
       </c>
       <c r="F2">
-        <v>4.2000000006782603</v>
+        <v>4.20000000067826</v>
       </c>
       <c r="G2">
-        <v>3217.8469344846699</v>
+        <v>3217.84693448467</v>
       </c>
       <c r="H2">
-        <v>24.435809152225801</v>
+        <v>24.4358091522258</v>
       </c>
       <c r="I2">
-        <v>23.069815375434398</v>
+        <v>23.0698153754344</v>
       </c>
       <c r="J2">
-        <v>21.816418424715799</v>
+        <v>21.8164184247158</v>
       </c>
       <c r="K2">
-        <v>5.3389591359982704</v>
+        <v>5.33895913599827</v>
       </c>
       <c r="L2">
         <v>18.1060049086277</v>
       </c>
       <c r="M2">
-        <v>-1.7168404732467699</v>
+        <v>-1.71684047324677</v>
       </c>
       <c r="N2">
         <v>-0.227864950895309</v>
       </c>
       <c r="O2">
-        <v>20.976063246416199</v>
+        <v>20.9760632464162</v>
       </c>
       <c r="P2">
         <v>46.2207217354077</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
-      <c r="B3" s="2"/>
       <c r="C3">
         <v>0.253001084795547</v>
       </c>
@@ -557,16 +533,16 @@
         <v>38</v>
       </c>
       <c r="E3">
-        <v>26.356660634568801</v>
+        <v>26.3566606345688</v>
       </c>
       <c r="F3">
-        <v>2.7000000001910398</v>
+        <v>2.70000000019104</v>
       </c>
       <c r="G3">
-        <v>2847.1519194590801</v>
+        <v>2847.15191945908</v>
       </c>
       <c r="H3">
-        <v>24.341292051798401</v>
+        <v>24.3412920517984</v>
       </c>
       <c r="I3">
         <v>24.0019951706408</v>
@@ -575,110 +551,110 @@
         <v>22.8142845512603</v>
       </c>
       <c r="K3">
-        <v>5.7018948304960899</v>
+        <v>5.70189483049609</v>
       </c>
       <c r="L3">
-        <v>16.801677207942099</v>
+        <v>16.8016772079421</v>
       </c>
       <c r="M3">
-        <v>-0.80192766400984705</v>
+        <v>-0.8019276640098471</v>
       </c>
       <c r="O3">
-        <v>21.700591426429501</v>
+        <v>21.7005914264295</v>
       </c>
       <c r="P3">
-        <v>49.170945185828998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+        <v>49.170945185829</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
       <c r="B4">
-        <v>0.33290150761604298</v>
+        <v>0.332901507616043</v>
       </c>
       <c r="C4">
-        <v>0.78193746470047898</v>
+        <v>0.781937464700479</v>
       </c>
       <c r="D4">
         <v>31.8</v>
       </c>
       <c r="E4">
-        <v>28.431167217680201</v>
+        <v>28.4311672176802</v>
       </c>
       <c r="F4">
-        <v>3.7003744040666802</v>
+        <v>3.70037440406668</v>
       </c>
       <c r="G4">
         <v>2688.23676032806</v>
       </c>
       <c r="H4">
-        <v>23.680378315185202</v>
+        <v>23.6803783151852</v>
       </c>
       <c r="I4">
-        <v>22.701675968225398</v>
+        <v>22.7016759682254</v>
       </c>
       <c r="J4">
         <v>25.0343344117566</v>
       </c>
       <c r="K4">
-        <v>9.4947137809959994</v>
+        <v>9.494713780995999</v>
       </c>
       <c r="L4">
         <v>14.5583370058408</v>
       </c>
       <c r="M4">
-        <v>-1.3920988102510701</v>
+        <v>-1.39209881025107</v>
       </c>
       <c r="N4">
         <v>-0.254789859056473</v>
       </c>
       <c r="O4">
-        <v>20.824892771235501</v>
+        <v>20.8248927712355</v>
       </c>
       <c r="P4">
-        <v>53.465501629436901</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+        <v>53.4655016294369</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
       <c r="B5">
-        <v>0.27554082870483398</v>
+        <v>0.275540828704834</v>
       </c>
       <c r="C5">
-        <v>-0.78244999226788303</v>
+        <v>-0.782449992267883</v>
       </c>
       <c r="D5">
         <v>31.5</v>
       </c>
       <c r="E5">
-        <v>23.915273361403401</v>
+        <v>23.9152733614034</v>
       </c>
       <c r="F5">
         <v>2.94907546754213</v>
       </c>
       <c r="G5">
-        <v>4062.2175599378602</v>
+        <v>4062.21755993786</v>
       </c>
       <c r="H5">
         <v>24.7704671599849</v>
       </c>
       <c r="I5">
-        <v>22.702490761056701</v>
+        <v>22.7024907610567</v>
       </c>
       <c r="J5">
-        <v>21.808589207575501</v>
+        <v>21.8085892075755</v>
       </c>
       <c r="K5">
-        <v>5.6794241406879999</v>
+        <v>5.679424140688</v>
       </c>
       <c r="L5">
         <v>12.5691941140716</v>
       </c>
       <c r="M5">
-        <v>-2.2645636858969098</v>
+        <v>-2.26456368589691</v>
       </c>
       <c r="N5">
         <v>-0.312842577695847</v>
@@ -687,18 +663,18 @@
         <v>20.4927670870354</v>
       </c>
       <c r="P5">
-        <v>45.723862568979001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+        <v>45.723862568979</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
       <c r="B6">
-        <v>0.39775311946868902</v>
+        <v>0.397753119468689</v>
       </c>
       <c r="C6">
-        <v>-2.5072612070361302</v>
+        <v>-2.50726120703613</v>
       </c>
       <c r="D6">
         <v>30.7</v>
@@ -707,98 +683,98 @@
         <v>22.7575187856654</v>
       </c>
       <c r="F6">
-        <v>4.5545599072177403</v>
+        <v>4.55455990721774</v>
       </c>
       <c r="G6">
-        <v>5221.4633373172101</v>
+        <v>5221.46333731721</v>
       </c>
       <c r="H6">
-        <v>25.602049777311301</v>
+        <v>25.6020497773113</v>
       </c>
       <c r="I6">
-        <v>24.080778820201399</v>
+        <v>24.0807788202014</v>
       </c>
       <c r="J6">
-        <v>22.886056438338699</v>
+        <v>22.8860564383387</v>
       </c>
       <c r="K6">
-        <v>-0.69203943785768895</v>
+        <v>-0.692039437857689</v>
       </c>
       <c r="L6">
-        <v>11.561326251545299</v>
+        <v>11.5613262515453</v>
       </c>
       <c r="M6">
-        <v>-1.6823666404509401</v>
+        <v>-1.68236664045094</v>
       </c>
       <c r="N6">
-        <v>-0.13172955811023701</v>
+        <v>-0.131729558110237</v>
       </c>
       <c r="O6">
         <v>21.6985960707513</v>
       </c>
       <c r="P6">
-        <v>45.643575224004103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+        <v>45.6435752240041</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
       <c r="B7">
-        <v>0.48385718464851402</v>
+        <v>0.483857184648514</v>
       </c>
       <c r="C7">
-        <v>-2.7747758989593998</v>
+        <v>-2.7747758989594</v>
       </c>
       <c r="D7">
         <v>29.6</v>
       </c>
       <c r="E7">
-        <v>23.599764491543599</v>
+        <v>23.5997644915436</v>
       </c>
       <c r="F7">
-        <v>5.2770519729546699</v>
+        <v>5.27705197295467</v>
       </c>
       <c r="G7">
-        <v>5836.8766332512696</v>
+        <v>5836.87663325127</v>
       </c>
       <c r="H7">
-        <v>25.601722701719201</v>
+        <v>25.6017227017192</v>
       </c>
       <c r="I7">
-        <v>25.730138500550101</v>
+        <v>25.7301385005501</v>
       </c>
       <c r="J7">
-        <v>23.828016905489299</v>
+        <v>23.8280169054893</v>
       </c>
       <c r="K7">
-        <v>2.0628530822342701</v>
+        <v>2.06285308223427</v>
       </c>
       <c r="L7">
         <v>10.8593590528679</v>
       </c>
       <c r="M7">
-        <v>-0.16183983464357399</v>
+        <v>-0.161839834643574</v>
       </c>
       <c r="N7">
         <v>-0.162092119455338</v>
       </c>
       <c r="O7">
-        <v>22.972111180598301</v>
+        <v>22.9721111805983</v>
       </c>
       <c r="P7">
-        <v>47.427781397032902</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+        <v>47.4277813970329</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
       <c r="B8">
-        <v>0.37827143073081998</v>
+        <v>0.37827143073082</v>
       </c>
       <c r="C8">
-        <v>-4.0001242759472797</v>
+        <v>-4.00012427594728</v>
       </c>
       <c r="D8">
         <v>28</v>
@@ -807,90 +783,90 @@
         <v>26.098249881712</v>
       </c>
       <c r="F8">
-        <v>5.6038064589588901</v>
+        <v>5.60380645895889</v>
       </c>
       <c r="G8">
-        <v>6077.3829338887599</v>
+        <v>6077.38293388876</v>
       </c>
       <c r="H8">
-        <v>25.841785281182698</v>
+        <v>25.8417852811827</v>
       </c>
       <c r="I8">
-        <v>26.929269060118099</v>
+        <v>26.9292690601181</v>
       </c>
       <c r="J8">
-        <v>27.669891392402601</v>
+        <v>27.6698913924026</v>
       </c>
       <c r="K8">
-        <v>3.2439076541922902</v>
+        <v>3.24390765419229</v>
       </c>
       <c r="L8">
-        <v>9.8503156742565192</v>
+        <v>9.850315674256519</v>
       </c>
       <c r="M8">
-        <v>0.78178691758824803</v>
+        <v>0.781786917588248</v>
       </c>
       <c r="N8">
-        <v>4.70300763845444E-2</v>
+        <v>0.0470300763845444</v>
       </c>
       <c r="O8">
         <v>24.3780853808343</v>
       </c>
       <c r="P8">
-        <v>53.768141274114498</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+        <v>53.7681412741145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
       <c r="B9">
-        <v>0.19767248630523701</v>
+        <v>0.197672486305237</v>
       </c>
       <c r="C9">
-        <v>-4.8618916070692597</v>
+        <v>-4.86189160706926</v>
       </c>
       <c r="D9">
         <v>24.3</v>
       </c>
       <c r="E9">
-        <v>27.958964394702001</v>
+        <v>27.958964394702</v>
       </c>
       <c r="F9">
         <v>5.36047405394162</v>
       </c>
       <c r="G9">
-        <v>6591.8553596056399</v>
+        <v>6591.85535960564</v>
       </c>
       <c r="H9">
-        <v>26.080541854020701</v>
+        <v>26.0805418540207</v>
       </c>
       <c r="I9">
-        <v>27.258305968797199</v>
+        <v>27.2583059687972</v>
       </c>
       <c r="J9">
-        <v>29.166174743045001</v>
+        <v>29.166174743045</v>
       </c>
       <c r="K9">
-        <v>6.1778121480938797</v>
+        <v>6.17781214809388</v>
       </c>
       <c r="L9">
-        <v>8.6730967502642908</v>
+        <v>8.673096750264291</v>
       </c>
       <c r="M9">
-        <v>0.92467991629409296</v>
+        <v>0.924679916294093</v>
       </c>
       <c r="N9">
         <v>0.215346544981003</v>
       </c>
       <c r="O9">
-        <v>24.807237282433601</v>
+        <v>24.8072372824336</v>
       </c>
       <c r="P9">
-        <v>57.125139137746999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+        <v>57.125139137747</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
@@ -898,7 +874,7 @@
         <v>0.153828725218773</v>
       </c>
       <c r="C10">
-        <v>-5.1861810846768002</v>
+        <v>-5.1861810846768</v>
       </c>
       <c r="D10">
         <v>24</v>
@@ -907,181 +883,181 @@
         <v>32.2546736710677</v>
       </c>
       <c r="F10">
-        <v>3.1910438863288002</v>
+        <v>3.1910438863288</v>
       </c>
       <c r="G10">
-        <v>6184.7547432839901</v>
+        <v>6184.75474328399</v>
       </c>
       <c r="H10">
-        <v>27.177118346408399</v>
+        <v>27.1771183464084</v>
       </c>
       <c r="I10">
-        <v>26.871294111050901</v>
+        <v>26.8712941110509</v>
       </c>
       <c r="J10">
-        <v>33.719850128555599</v>
+        <v>33.7198501285556</v>
       </c>
       <c r="K10">
-        <v>9.9099845600546708</v>
+        <v>9.909984560054671</v>
       </c>
       <c r="L10">
-        <v>7.6976073804605996</v>
+        <v>7.6976073804606</v>
       </c>
       <c r="M10">
-        <v>-0.58909551283027495</v>
+        <v>-0.5890955128302749</v>
       </c>
       <c r="N10">
-        <v>4.9528993666172E-2</v>
+        <v>0.049528993666172</v>
       </c>
       <c r="O10">
-        <v>24.322809870073002</v>
+        <v>24.322809870073</v>
       </c>
       <c r="P10">
-        <v>65.974523799623299</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+        <v>65.9745237996233</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
       <c r="B11">
-        <v>0.12542669475078599</v>
+        <v>0.125426694750786</v>
       </c>
       <c r="C11">
-        <v>-2.3845818736153199</v>
+        <v>-2.38458187361532</v>
       </c>
       <c r="D11">
         <v>27</v>
       </c>
       <c r="E11">
-        <v>24.982746488323698</v>
+        <v>24.9827464883237</v>
       </c>
       <c r="F11">
-        <v>-1.5380891352558299</v>
+        <v>-1.53808913525583</v>
       </c>
       <c r="G11">
-        <v>6374.7056004299202</v>
+        <v>6374.70560042992</v>
       </c>
       <c r="H11">
-        <v>29.101903370675899</v>
+        <v>29.1019033706759</v>
       </c>
       <c r="I11">
-        <v>24.996539087393899</v>
+        <v>24.9965390873939</v>
       </c>
       <c r="J11">
-        <v>24.604788839556399</v>
+        <v>24.6047888395564</v>
       </c>
       <c r="K11">
-        <v>7.2380952380952701</v>
+        <v>7.23809523809527</v>
       </c>
       <c r="L11">
         <v>7.31227235926203</v>
       </c>
       <c r="M11">
-        <v>-4.4645084849093797</v>
+        <v>-4.46450848490938</v>
       </c>
       <c r="N11">
         <v>-0.114492610096931</v>
       </c>
       <c r="O11">
-        <v>21.894874300616198</v>
+        <v>21.8948743006162</v>
       </c>
       <c r="P11">
-        <v>49.587535327880097</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+        <v>49.5875353278801</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
       <c r="B12">
-        <v>6.5393097698688493E-2</v>
+        <v>0.06539309769868849</v>
       </c>
       <c r="C12">
-        <v>-1.2990180561559601</v>
+        <v>-1.29901805615596</v>
       </c>
       <c r="D12">
         <v>31.2</v>
       </c>
       <c r="E12">
-        <v>25.783417626722098</v>
+        <v>25.7834176267221</v>
       </c>
       <c r="F12">
-        <v>3.0397328812795599</v>
+        <v>3.03973288127956</v>
       </c>
       <c r="G12">
         <v>7973.47195771517</v>
       </c>
       <c r="H12">
-        <v>29.577512826076902</v>
+        <v>29.5775128260769</v>
       </c>
       <c r="I12">
-        <v>25.519226716585798</v>
+        <v>25.5192267165858</v>
       </c>
       <c r="J12">
-        <v>24.622669535877801</v>
+        <v>24.6226695358778</v>
       </c>
       <c r="K12">
-        <v>4.0674955595026399</v>
+        <v>4.06749555950264</v>
       </c>
       <c r="L12">
-        <v>7.6801909701960396</v>
+        <v>7.68019097019604</v>
       </c>
       <c r="M12">
-        <v>-4.4426726598709498</v>
+        <v>-4.44267265987095</v>
       </c>
       <c r="N12">
-        <v>-2.9427003115415601E-2</v>
+        <v>-0.0294270031154156</v>
       </c>
       <c r="O12">
-        <v>22.520603877613201</v>
+        <v>22.5206038776132</v>
       </c>
       <c r="P12">
-        <v>50.406087162599903</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+        <v>50.4060871625999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
       <c r="B13">
-        <v>-4.2337053455412397E-3</v>
+        <v>-0.00423370534554124</v>
       </c>
       <c r="C13">
-        <v>-2.0196762851327401</v>
+        <v>-2.01967628513274</v>
       </c>
       <c r="D13">
-        <v>34.700000000000003</v>
+        <v>34.7</v>
       </c>
       <c r="E13">
-        <v>27.698148470375202</v>
+        <v>27.6981484703752</v>
       </c>
       <c r="F13">
-        <v>3.1685562785881798</v>
+        <v>3.16855627858818</v>
       </c>
       <c r="G13">
-        <v>8646.0557107163495</v>
+        <v>8646.055710716349</v>
       </c>
       <c r="H13">
-        <v>31.061973446417099</v>
+        <v>31.0619734464171</v>
       </c>
       <c r="I13">
-        <v>25.974054755098699</v>
+        <v>25.9740547550987</v>
       </c>
       <c r="J13">
-        <v>26.938201965521898</v>
+        <v>26.9382019655219</v>
       </c>
       <c r="K13">
-        <v>5.0008533879501904</v>
+        <v>5.00085338795019</v>
       </c>
       <c r="L13">
-        <v>7.9037627628616898</v>
+        <v>7.90376276286169</v>
       </c>
       <c r="M13">
-        <v>-5.4620632975257299</v>
+        <v>-5.46206329752573</v>
       </c>
       <c r="N13">
-        <v>2.40315701812506E-2</v>
+        <v>0.0240315701812506</v>
       </c>
       <c r="O13">
         <v>22.8746700116825</v>
@@ -1090,57 +1066,57 @@
         <v>54.6363504358971</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
       <c r="B14">
-        <v>-0.18417060375213601</v>
+        <v>-0.184170603752136</v>
       </c>
       <c r="C14">
-        <v>-4.6837364340384804</v>
+        <v>-4.68373643403848</v>
       </c>
       <c r="D14">
         <v>37.4</v>
       </c>
       <c r="E14">
-        <v>27.139149193767899</v>
+        <v>27.1391491937679</v>
       </c>
       <c r="F14">
-        <v>2.3962323846574498</v>
+        <v>2.39623238465745</v>
       </c>
       <c r="G14">
-        <v>8076.9767847974099</v>
+        <v>8076.97678479741</v>
       </c>
       <c r="H14">
-        <v>30.365179734174301</v>
+        <v>30.3651797341743</v>
       </c>
       <c r="I14">
-        <v>26.522785683462502</v>
+        <v>26.5227856834625</v>
       </c>
       <c r="J14">
         <v>28.4434679995666</v>
       </c>
       <c r="K14">
-        <v>5.7379713914173696</v>
+        <v>5.73797139141737</v>
       </c>
       <c r="L14">
-        <v>8.7038710886433996</v>
+        <v>8.7038710886434</v>
       </c>
       <c r="M14">
-        <v>-4.2320930867363797</v>
+        <v>-4.23209308673638</v>
       </c>
       <c r="N14">
-        <v>-2.5386700406670602E-2</v>
+        <v>-0.0253867004066706</v>
       </c>
       <c r="O14">
-        <v>23.345765989473598</v>
+        <v>23.3457659894736</v>
       </c>
       <c r="P14">
-        <v>55.582617193334499</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+        <v>55.5826171933345</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
@@ -1148,104 +1124,104 @@
         <v>-0.138074696063995</v>
       </c>
       <c r="C15">
-        <v>-5.3383727475691103</v>
+        <v>-5.33837274756911</v>
       </c>
       <c r="D15">
         <v>40.4</v>
       </c>
       <c r="E15">
-        <v>28.379280320361001</v>
+        <v>28.379280320361</v>
       </c>
       <c r="F15">
         <v>2.48546800826588</v>
       </c>
       <c r="G15">
-        <v>7331.6546738491897</v>
+        <v>7331.65467384919</v>
       </c>
       <c r="H15">
-        <v>31.259190573784998</v>
+        <v>31.259190573785</v>
       </c>
       <c r="I15">
         <v>27.4101862231804</v>
       </c>
       <c r="J15">
-        <v>30.495747309690099</v>
+        <v>30.4957473096901</v>
       </c>
       <c r="K15">
-        <v>5.7801691006917704</v>
+        <v>5.78016910069177</v>
       </c>
       <c r="L15">
-        <v>8.7377553373175392</v>
+        <v>8.737755337317539</v>
       </c>
       <c r="M15">
-        <v>-4.1829931080396303</v>
+        <v>-4.18299310803963</v>
       </c>
       <c r="N15">
-        <v>-4.6294536441564602E-2</v>
+        <v>-0.0462945364415646</v>
       </c>
       <c r="O15">
-        <v>23.831391363238001</v>
+        <v>23.831391363238</v>
       </c>
       <c r="P15">
-        <v>58.875027630051001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+        <v>58.875027630051</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
       <c r="B16">
-        <v>-0.12528701126575501</v>
+        <v>-0.125287011265755</v>
       </c>
       <c r="C16">
-        <v>-4.8124325948848297</v>
+        <v>-4.81243259488483</v>
       </c>
       <c r="D16">
         <v>43.3</v>
       </c>
       <c r="E16">
-        <v>29.000619303347101</v>
+        <v>29.0006193033471</v>
       </c>
       <c r="F16">
         <v>1.41382645223793</v>
       </c>
       <c r="G16">
-        <v>6856.7313709252203</v>
+        <v>6856.73137092522</v>
       </c>
       <c r="H16">
         <v>31.9053501556958</v>
       </c>
       <c r="I16">
-        <v>28.872613056716499</v>
+        <v>28.8726130567165</v>
       </c>
       <c r="J16">
-        <v>30.498954751712098</v>
+        <v>30.4989547517121</v>
       </c>
       <c r="K16">
-        <v>6.1328295305914899</v>
+        <v>6.13282953059149</v>
       </c>
       <c r="L16">
-        <v>9.1794133411094094</v>
+        <v>9.179413341109409</v>
       </c>
       <c r="M16">
         <v>-3.43956150956061</v>
       </c>
       <c r="N16">
-        <v>-0.14638896286487599</v>
+        <v>-0.146388962864876</v>
       </c>
       <c r="O16">
-        <v>24.431934217603398</v>
+        <v>24.4319342176034</v>
       </c>
       <c r="P16">
-        <v>59.499574055059298</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+        <v>59.4995740550593</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
       <c r="B17">
-        <v>-7.0839747786521898E-2</v>
+        <v>-0.0708397477865219</v>
       </c>
       <c r="C17">
         <v>-4.31028688643788</v>
@@ -1254,101 +1230,101 @@
         <v>45.2</v>
       </c>
       <c r="E17">
-        <v>27.713638412482901</v>
+        <v>27.7136384124829</v>
       </c>
       <c r="F17">
-        <v>1.3218622367822901</v>
+        <v>1.32186223678229</v>
       </c>
       <c r="G17">
-        <v>6112.2738248597398</v>
+        <v>6112.27382485974</v>
       </c>
       <c r="H17">
-        <v>33.679778745490701</v>
+        <v>33.6797787454907</v>
       </c>
       <c r="I17">
-        <v>29.647258188711199</v>
+        <v>29.6472581887112</v>
       </c>
       <c r="J17">
         <v>29.0130377322327</v>
       </c>
       <c r="K17">
-        <v>4.5186909489250997</v>
+        <v>4.5186909489251</v>
       </c>
       <c r="L17">
-        <v>9.0989650999005391</v>
+        <v>9.098965099900539</v>
       </c>
       <c r="M17">
-        <v>-4.5643766355589399</v>
+        <v>-4.56437663555894</v>
       </c>
       <c r="N17">
         <v>-0.220544874668121</v>
       </c>
       <c r="O17">
-        <v>25.048692703114401</v>
+        <v>25.0486927031144</v>
       </c>
       <c r="P17">
-        <v>56.726676144715597</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+        <v>56.7266761447156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
       <c r="B18">
-        <v>1.7026288434863101E-2</v>
+        <v>0.0170262884348631</v>
       </c>
       <c r="C18">
-        <v>-2.6336145167879801</v>
+        <v>-2.63361451678798</v>
       </c>
       <c r="D18">
         <v>47.1</v>
       </c>
       <c r="E18">
-        <v>28.156088169895501</v>
+        <v>28.1560881698955</v>
       </c>
       <c r="F18">
-        <v>0.66455230785811603</v>
+        <v>0.664552307858116</v>
       </c>
       <c r="G18">
-        <v>5651.2058516574898</v>
+        <v>5651.20585165749</v>
       </c>
       <c r="H18">
-        <v>32.189660800211101</v>
+        <v>32.1896608002111</v>
       </c>
       <c r="I18">
-        <v>29.040659001519501</v>
+        <v>29.0406590015195</v>
       </c>
       <c r="J18">
-        <v>27.705169334982699</v>
+        <v>27.7051693349827</v>
       </c>
       <c r="K18">
-        <v>6.6029084239486897</v>
+        <v>6.60290842394869</v>
       </c>
       <c r="L18">
-        <v>10.215019680071601</v>
+        <v>10.2150196800716</v>
       </c>
       <c r="M18">
-        <v>-3.4604987446604301</v>
+        <v>-3.46049874466043</v>
       </c>
       <c r="N18">
-        <v>-0.14908500015735601</v>
+        <v>-0.149085000157356</v>
       </c>
       <c r="O18">
         <v>24.8283559884696</v>
       </c>
       <c r="P18">
-        <v>55.861257504878203</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+        <v>55.8612575048782</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
       <c r="B19">
-        <v>-0.12777316570281999</v>
+        <v>-0.12777316570282</v>
       </c>
       <c r="C19">
-        <v>-2.3743675318864899</v>
+        <v>-2.37436753188649</v>
       </c>
       <c r="D19">
         <v>48.6</v>
@@ -1360,28 +1336,28 @@
         <v>1.15794695181735</v>
       </c>
       <c r="G19">
-        <v>6618.3350825570096</v>
+        <v>6618.33508255701</v>
       </c>
       <c r="H19">
-        <v>33.251812476877298</v>
+        <v>33.2518124768773</v>
       </c>
       <c r="I19">
-        <v>28.913155819620599</v>
+        <v>28.9131558196206</v>
       </c>
       <c r="J19">
         <v>26.1958560481525</v>
       </c>
       <c r="K19">
-        <v>5.1861865552414601</v>
+        <v>5.18618655524146</v>
       </c>
       <c r="L19">
         <v>10.5634519284442</v>
       </c>
       <c r="M19">
-        <v>-4.6575444774339196</v>
+        <v>-4.65754447743392</v>
       </c>
       <c r="N19">
-        <v>-0.28480362892150901</v>
+        <v>-0.284803628921509</v>
       </c>
       <c r="O19">
         <v>24.76928728931</v>
@@ -1390,62 +1366,62 @@
         <v>53.5359318293741</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
       <c r="B20">
-        <v>-0.13679742813110399</v>
+        <v>-0.136797428131104</v>
       </c>
       <c r="C20">
-        <v>-3.0005193942657602</v>
+        <v>-3.00051939426576</v>
       </c>
       <c r="D20">
         <v>51.5</v>
       </c>
       <c r="E20">
-        <v>27.497037150842299</v>
+        <v>27.4970371508423</v>
       </c>
       <c r="F20">
-        <v>1.5567838472167601</v>
+        <v>1.55678384721676</v>
       </c>
       <c r="G20">
-        <v>6914.1780318075998</v>
+        <v>6914.1780318076</v>
       </c>
       <c r="H20">
-        <v>33.995497825497203</v>
+        <v>33.9954978254972</v>
       </c>
       <c r="I20">
-        <v>28.364336831890199</v>
+        <v>28.3643368318902</v>
       </c>
       <c r="J20">
-        <v>26.988507976791698</v>
+        <v>26.9885079767917</v>
       </c>
       <c r="K20">
-        <v>4.5098726486739302</v>
+        <v>4.50987264867393</v>
       </c>
       <c r="L20">
-        <v>10.562564040785301</v>
+        <v>10.5625640407853</v>
       </c>
       <c r="M20">
-        <v>-5.6955139724721402</v>
+        <v>-5.69551397247214</v>
       </c>
       <c r="N20">
         <v>-0.237546816468239</v>
       </c>
       <c r="O20">
-        <v>24.894894072742201</v>
+        <v>24.8948940727422</v>
       </c>
       <c r="P20">
-        <v>54.485545127634097</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+        <v>54.4855451276341</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
       <c r="B21">
-        <v>-3.1280990689992898E-2</v>
+        <v>-0.0312809906899929</v>
       </c>
       <c r="C21">
         <v>-2.6199906748304</v>
@@ -1454,66 +1430,66 @@
         <v>56.1</v>
       </c>
       <c r="E21">
-        <v>27.202129405115102</v>
+        <v>27.2021294051151</v>
       </c>
       <c r="F21">
-        <v>0.25993557687633001</v>
+        <v>0.25993557687633</v>
       </c>
       <c r="G21">
-        <v>6533.7112103285599</v>
+        <v>6533.71121032856</v>
       </c>
       <c r="H21">
-        <v>34.653275461787203</v>
+        <v>34.6532754617872</v>
       </c>
       <c r="I21">
-        <v>28.897615749940201</v>
+        <v>28.8976157499402</v>
       </c>
       <c r="J21">
-        <v>26.695867003025501</v>
+        <v>26.6958670030255</v>
       </c>
       <c r="K21">
-        <v>4.1028507546114996</v>
+        <v>4.1028507546115</v>
       </c>
       <c r="L21">
-        <v>11.041411159620999</v>
+        <v>11.041411159621</v>
       </c>
       <c r="M21">
-        <v>-5.7519270389699999</v>
+        <v>-5.75192703897</v>
       </c>
       <c r="N21">
         <v>-0.2832210958004</v>
       </c>
       <c r="O21">
-        <v>24.867345326797601</v>
+        <v>24.8673453267976</v>
       </c>
       <c r="P21">
         <v>53.8979964081406</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
       <c r="B22">
-        <v>-5.9475705027580303E-2</v>
+        <v>-0.0594757050275803</v>
       </c>
       <c r="C22">
         <v>2.00352275153333</v>
       </c>
       <c r="D22">
-        <v>68.900000000000006</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E22">
-        <v>27.575914160396302</v>
+        <v>27.5759141603963</v>
       </c>
       <c r="F22">
-        <v>-6.1689177146757004</v>
+        <v>-6.1689177146757</v>
       </c>
       <c r="G22">
-        <v>5580.6038307518902</v>
+        <v>5580.60383075189</v>
       </c>
       <c r="H22">
-        <v>37.835416201174503</v>
+        <v>37.8354162011745</v>
       </c>
       <c r="I22">
         <v>27.8138753889078</v>
@@ -1522,83 +1498,83 @@
         <v>23.1837449200214</v>
       </c>
       <c r="K22">
-        <v>3.2323883161511899</v>
+        <v>3.23238831615119</v>
       </c>
       <c r="L22">
-        <v>11.429757261214601</v>
+        <v>11.4297572612146</v>
       </c>
       <c r="M22">
-        <v>-9.9266487239327397</v>
+        <v>-9.92664872393274</v>
       </c>
       <c r="N22">
         <v>-0.252867221832275</v>
       </c>
       <c r="O22">
-        <v>23.264944040919499</v>
+        <v>23.2649440409195</v>
       </c>
       <c r="P22">
-        <v>50.759659080417698</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+        <v>50.7596590804177</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
       <c r="B23">
-        <v>-3.4169111400842701E-2</v>
+        <v>-0.0341691114008427</v>
       </c>
       <c r="C23">
-        <v>3.7643416662577902</v>
+        <v>3.76434166625779</v>
       </c>
       <c r="D23">
         <v>68.8</v>
       </c>
       <c r="E23">
-        <v>31.103598806188302</v>
+        <v>31.1035988061883</v>
       </c>
       <c r="F23">
-        <v>4.9550325944075597</v>
+        <v>4.95503259440756</v>
       </c>
       <c r="G23">
         <v>6843.39941886204</v>
       </c>
       <c r="H23">
-        <v>34.531008884309998</v>
+        <v>34.53100888431</v>
       </c>
       <c r="I23">
         <v>30.0652667080962</v>
       </c>
       <c r="J23">
-        <v>24.931115031051601</v>
+        <v>24.9311150310516</v>
       </c>
       <c r="K23">
-        <v>4.6187454488713602</v>
+        <v>4.61874544887136</v>
       </c>
       <c r="L23">
         <v>12.92388692824</v>
       </c>
       <c r="M23">
-        <v>-4.4956873745965096</v>
+        <v>-4.49568737459651</v>
       </c>
       <c r="N23">
-        <v>-0.75098145008087203</v>
+        <v>-0.750981450080872</v>
       </c>
       <c r="O23">
-        <v>25.894627325285398</v>
+        <v>25.8946273252854</v>
       </c>
       <c r="P23">
-        <v>56.034713837239899</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+        <v>56.0347138372399</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
       <c r="B24">
-        <v>-0.33009460568428001</v>
+        <v>-0.33009460568428</v>
       </c>
       <c r="C24">
-        <v>-0.29667466248737201</v>
+        <v>-0.296674662487372</v>
       </c>
       <c r="D24">
         <v>70.7</v>
@@ -1607,116 +1583,107 @@
         <v>33.3714495540545</v>
       </c>
       <c r="F24">
-        <v>1.9114799603350401</v>
+        <v>1.91147996033504</v>
       </c>
       <c r="G24">
-        <v>6523.4109781585303</v>
+        <v>6523.41097815853</v>
       </c>
       <c r="H24">
-        <v>33.479835257817797</v>
+        <v>33.4798352578178</v>
       </c>
       <c r="I24">
-        <v>30.273151278644999</v>
+        <v>30.273151278645</v>
       </c>
       <c r="J24">
         <v>31.4115525789563</v>
       </c>
       <c r="K24">
-        <v>7.0398727254648099</v>
+        <v>7.03987272546481</v>
       </c>
       <c r="L24">
         <v>14.135856781628</v>
       </c>
       <c r="M24">
-        <v>-3.5216324926909399</v>
+        <v>-3.52163249269094</v>
       </c>
       <c r="N24">
-        <v>-0.68138635158538796</v>
+        <v>-0.681386351585388</v>
       </c>
       <c r="O24">
-        <v>26.005459782242799</v>
+        <v>26.0054597822428</v>
       </c>
       <c r="P24">
-        <v>64.783002133010797</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+        <v>64.7830021330108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
       <c r="B25">
-        <v>-0.28467044234275801</v>
+        <v>-0.284670442342758</v>
       </c>
       <c r="C25">
-        <v>-1.1057124296538201</v>
+        <v>-1.10571242965382</v>
       </c>
       <c r="D25">
         <v>73.2</v>
       </c>
       <c r="E25">
-        <v>32.754526867542403</v>
+        <v>32.7545268675424</v>
       </c>
       <c r="F25">
-        <v>0.69848519372483497</v>
+        <v>0.698485193724835</v>
       </c>
       <c r="G25">
-        <v>6022.5425419233497</v>
-      </c>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
+        <v>6022.54254192335</v>
+      </c>
       <c r="J25">
         <v>32.4255686814627</v>
       </c>
       <c r="K25">
-        <v>6.0752438457965603</v>
-      </c>
-      <c r="L25" s="2"/>
+        <v>6.07524384579656</v>
+      </c>
       <c r="M25">
         <v>-5.5</v>
       </c>
       <c r="N25">
-        <v>-0.66564202308654796</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>-0.665642023086548</v>
+      </c>
       <c r="P25">
-        <v>65.180095549005102</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+        <v>65.1800955490051</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
-      <c r="B26" s="2"/>
       <c r="C26">
-        <v>-0.64421989954371806</v>
+        <v>-0.6442198995437181</v>
       </c>
       <c r="D26">
         <v>76</v>
       </c>
       <c r="E26">
-        <v>31.849845185990102</v>
+        <v>31.8498451859901</v>
       </c>
       <c r="F26">
-        <v>0.57985369230391404</v>
+        <v>0.579853692303914</v>
       </c>
       <c r="G26">
-        <v>6253.3715819454301</v>
-      </c>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
+        <v>6253.37158194543</v>
+      </c>
       <c r="J26">
         <v>29.8527528715858</v>
       </c>
       <c r="K26">
-        <v>4.3611524651896296</v>
-      </c>
-      <c r="L26" s="2"/>
+        <v>4.36115246518963</v>
+      </c>
       <c r="M26">
         <v>-5.8</v>
       </c>
-      <c r="O26" s="2"/>
       <c r="P26">
-        <v>61.702598057575898</v>
+        <v>61.7025980575759</v>
       </c>
     </row>
   </sheetData>
